--- a/research/traditional_assets/database/data/turkey/turkey_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_software_entertainment.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1858250907705051</v>
+        <v>0.1853942780435789</v>
       </c>
       <c r="C2">
-        <v>75.70207017518291</v>
+        <v>75.17213836997325</v>
       </c>
       <c r="D2">
-        <v>73.59207017518291</v>
+        <v>73.81918836997326</v>
       </c>
       <c r="E2">
-        <v>-0.105</v>
+        <v>0.65205</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.75705</v>
       </c>
       <c r="G2">
         <v>2.11</v>
@@ -1439,28 +1439,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.038079615</v>
       </c>
       <c r="N2">
-        <v>8.380000000000001</v>
+        <v>8.341920385000002</v>
       </c>
       <c r="O2">
-        <v>2.095</v>
+        <v>2.08548009625</v>
       </c>
       <c r="P2">
-        <v>6.285</v>
+        <v>6.256440288750001</v>
       </c>
       <c r="Q2">
-        <v>6.885</v>
+        <v>6.856440288750001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1858250907705051</v>
+        <v>0.1868858869127059</v>
       </c>
       <c r="T2">
-        <v>1.354149646462541</v>
+        <v>1.364408355905439</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>220.065250134488</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1853942780435789</v>
+        <v>0.1849634653166526</v>
       </c>
       <c r="C3">
-        <v>75.17213836997325</v>
+        <v>74.64361275867533</v>
       </c>
       <c r="D3">
-        <v>73.81918836997326</v>
+        <v>74.04771275867533</v>
       </c>
       <c r="E3">
-        <v>0.65205</v>
+        <v>1.4091</v>
       </c>
       <c r="F3">
-        <v>0.75705</v>
+        <v>1.5141</v>
       </c>
       <c r="G3">
         <v>2.11</v>
@@ -1521,28 +1521,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M3">
-        <v>0.038079615</v>
+        <v>0.07615922999999999</v>
       </c>
       <c r="N3">
-        <v>8.341920385000002</v>
+        <v>8.303840770000001</v>
       </c>
       <c r="O3">
-        <v>2.08548009625</v>
+        <v>2.0759601925</v>
       </c>
       <c r="P3">
-        <v>6.256440288750001</v>
+        <v>6.227880577500001</v>
       </c>
       <c r="Q3">
-        <v>6.856440288750001</v>
+        <v>6.8278805775</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1868858869127059</v>
+        <v>0.187968331955768</v>
       </c>
       <c r="T3">
-        <v>1.364408355905439</v>
+        <v>1.374876426765539</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>220.065250134488</v>
+        <v>110.032625067244</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1849634653166526</v>
+        <v>0.1845326525897263</v>
       </c>
       <c r="C4">
-        <v>74.64361275867533</v>
+        <v>74.11650644144019</v>
       </c>
       <c r="D4">
-        <v>74.04771275867533</v>
+        <v>74.2776564414402</v>
       </c>
       <c r="E4">
-        <v>1.4091</v>
+        <v>2.16615</v>
       </c>
       <c r="F4">
-        <v>1.5141</v>
+        <v>2.27115</v>
       </c>
       <c r="G4">
         <v>2.11</v>
@@ -1603,28 +1603,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M4">
-        <v>0.07615922999999999</v>
+        <v>0.114238845</v>
       </c>
       <c r="N4">
-        <v>8.303840770000001</v>
+        <v>8.265761155000002</v>
       </c>
       <c r="O4">
-        <v>2.0759601925</v>
+        <v>2.06644028875</v>
       </c>
       <c r="P4">
-        <v>6.227880577500001</v>
+        <v>6.199320866250002</v>
       </c>
       <c r="Q4">
-        <v>6.8278805775</v>
+        <v>6.799320866250001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.187968331955768</v>
+        <v>0.1890730954533261</v>
       </c>
       <c r="T4">
-        <v>1.374876426765539</v>
+        <v>1.385560334138218</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>110.032625067244</v>
+        <v>73.35508337816267</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1845326525897263</v>
+        <v>0.1841018398628001</v>
       </c>
       <c r="C5">
-        <v>74.11650644144019</v>
+        <v>73.59083268164764</v>
       </c>
       <c r="D5">
-        <v>74.2776564414402</v>
+        <v>74.50903268164764</v>
       </c>
       <c r="E5">
-        <v>2.16615</v>
+        <v>2.9232</v>
       </c>
       <c r="F5">
-        <v>2.27115</v>
+        <v>3.0282</v>
       </c>
       <c r="G5">
         <v>2.11</v>
@@ -1685,28 +1685,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M5">
-        <v>0.114238845</v>
+        <v>0.15231846</v>
       </c>
       <c r="N5">
-        <v>8.265761155000002</v>
+        <v>8.227681540000001</v>
       </c>
       <c r="O5">
-        <v>2.06644028875</v>
+        <v>2.056920385</v>
       </c>
       <c r="P5">
-        <v>6.199320866250002</v>
+        <v>6.170761155000001</v>
       </c>
       <c r="Q5">
-        <v>6.799320866250001</v>
+        <v>6.770761155000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1890730954533261</v>
+        <v>0.1902008748570834</v>
       </c>
       <c r="T5">
-        <v>1.385560334138218</v>
+        <v>1.396466822914495</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.35508337816267</v>
+        <v>55.016312533622</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1841018398628001</v>
+        <v>0.1836710271358738</v>
       </c>
       <c r="C6">
-        <v>73.59083268164764</v>
+        <v>73.06660490845665</v>
       </c>
       <c r="D6">
-        <v>74.50903268164764</v>
+        <v>74.74185490845666</v>
       </c>
       <c r="E6">
-        <v>2.9232</v>
+        <v>3.68025</v>
       </c>
       <c r="F6">
-        <v>3.0282</v>
+        <v>3.78525</v>
       </c>
       <c r="G6">
         <v>2.11</v>
@@ -1767,28 +1767,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M6">
-        <v>0.15231846</v>
+        <v>0.190398075</v>
       </c>
       <c r="N6">
-        <v>8.227681540000001</v>
+        <v>8.189601925000002</v>
       </c>
       <c r="O6">
-        <v>2.056920385</v>
+        <v>2.04740048125</v>
       </c>
       <c r="P6">
-        <v>6.170761155000001</v>
+        <v>6.142201443750001</v>
       </c>
       <c r="Q6">
-        <v>6.770761155000001</v>
+        <v>6.742201443750001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1902008748570834</v>
+        <v>0.1913523969851303</v>
       </c>
       <c r="T6">
-        <v>1.396466822914495</v>
+        <v>1.407602921980799</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.016312533622</v>
+        <v>44.0130500268976</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1836710271358738</v>
+        <v>0.1832402144089475</v>
       </c>
       <c r="C7">
-        <v>73.06660490845665</v>
+        <v>72.54383671940342</v>
       </c>
       <c r="D7">
-        <v>74.74185490845666</v>
+        <v>74.97613671940341</v>
       </c>
       <c r="E7">
-        <v>3.68025</v>
+        <v>4.4373</v>
       </c>
       <c r="F7">
-        <v>3.78525</v>
+        <v>4.5423</v>
       </c>
       <c r="G7">
         <v>2.11</v>
@@ -1849,28 +1849,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M7">
-        <v>0.190398075</v>
+        <v>0.22847769</v>
       </c>
       <c r="N7">
-        <v>8.189601925000002</v>
+        <v>8.151522310000001</v>
       </c>
       <c r="O7">
-        <v>2.04740048125</v>
+        <v>2.0378805775</v>
       </c>
       <c r="P7">
-        <v>6.142201443750001</v>
+        <v>6.113641732500001</v>
       </c>
       <c r="Q7">
-        <v>6.742201443750001</v>
+        <v>6.7136417325</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1913523969851303</v>
+        <v>0.1925284195839867</v>
       </c>
       <c r="T7">
-        <v>1.407602921980799</v>
+        <v>1.418975959325109</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.0130500268976</v>
+        <v>36.67754168908133</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1832402144089475</v>
+        <v>0.1828094016820213</v>
       </c>
       <c r="C8">
-        <v>72.54383671940342</v>
+        <v>72.02254188304866</v>
       </c>
       <c r="D8">
-        <v>74.97613671940341</v>
+        <v>75.21189188304866</v>
       </c>
       <c r="E8">
-        <v>4.4373</v>
+        <v>5.194349999999999</v>
       </c>
       <c r="F8">
-        <v>4.5423</v>
+        <v>5.29935</v>
       </c>
       <c r="G8">
         <v>2.11</v>
@@ -1931,28 +1931,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M8">
-        <v>0.22847769</v>
+        <v>0.266557305</v>
       </c>
       <c r="N8">
-        <v>8.151522310000001</v>
+        <v>8.113442695000002</v>
       </c>
       <c r="O8">
-        <v>2.0378805775</v>
+        <v>2.02836067375</v>
       </c>
       <c r="P8">
-        <v>6.113641732500001</v>
+        <v>6.085082021250001</v>
       </c>
       <c r="Q8">
-        <v>6.7136417325</v>
+        <v>6.68508202125</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1925284195839867</v>
+        <v>0.1937297329914207</v>
       </c>
       <c r="T8">
-        <v>1.418975959325109</v>
+        <v>1.430593578117684</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.67754168908133</v>
+        <v>31.43789287635543</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1828094016820213</v>
+        <v>0.182378588955095</v>
       </c>
       <c r="C9">
-        <v>72.02254188304866</v>
+        <v>71.50273434167498</v>
       </c>
       <c r="D9">
-        <v>75.21189188304866</v>
+        <v>75.44913434167498</v>
       </c>
       <c r="E9">
-        <v>5.19435</v>
+        <v>5.9514</v>
       </c>
       <c r="F9">
-        <v>5.29935</v>
+        <v>6.0564</v>
       </c>
       <c r="G9">
         <v>2.11</v>
@@ -2013,28 +2013,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M9">
-        <v>0.266557305</v>
+        <v>0.30463692</v>
       </c>
       <c r="N9">
-        <v>8.113442695000002</v>
+        <v>8.075363080000001</v>
       </c>
       <c r="O9">
-        <v>2.02836067375</v>
+        <v>2.01884077</v>
       </c>
       <c r="P9">
-        <v>6.085082021250001</v>
+        <v>6.05652231</v>
       </c>
       <c r="Q9">
-        <v>6.68508202125</v>
+        <v>6.65652231</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1937297329914207</v>
+        <v>0.194957161907712</v>
       </c>
       <c r="T9">
-        <v>1.430593578117684</v>
+        <v>1.442463753840533</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.43789287635543</v>
+        <v>27.508156266811</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.182378588955095</v>
+        <v>0.1819477762281687</v>
       </c>
       <c r="C10">
-        <v>71.50273434167498</v>
+        <v>70.98442821403533</v>
       </c>
       <c r="D10">
-        <v>75.44913434167498</v>
+        <v>75.68787821403534</v>
       </c>
       <c r="E10">
-        <v>5.9514</v>
+        <v>6.708449999999999</v>
       </c>
       <c r="F10">
-        <v>6.0564</v>
+        <v>6.81345</v>
       </c>
       <c r="G10">
         <v>2.11</v>
@@ -2095,28 +2095,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M10">
-        <v>0.30463692</v>
+        <v>0.3427165349999999</v>
       </c>
       <c r="N10">
-        <v>8.075363080000001</v>
+        <v>8.037283465000002</v>
       </c>
       <c r="O10">
-        <v>2.01884077</v>
+        <v>2.00932086625</v>
       </c>
       <c r="P10">
-        <v>6.05652231</v>
+        <v>6.027962598750001</v>
       </c>
       <c r="Q10">
-        <v>6.65652231</v>
+        <v>6.627962598750001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.194957161907712</v>
+        <v>0.1962115672837019</v>
       </c>
       <c r="T10">
-        <v>1.442463753840533</v>
+        <v>1.454594812546301</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.508156266811</v>
+        <v>24.45169445938756</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1819477762281687</v>
+        <v>0.1815169635012425</v>
       </c>
       <c r="C11">
-        <v>70.98442821403533</v>
+        <v>70.46763779815394</v>
       </c>
       <c r="D11">
-        <v>75.68787821403534</v>
+        <v>75.92813779815394</v>
       </c>
       <c r="E11">
-        <v>6.708449999999999</v>
+        <v>7.465499999999999</v>
       </c>
       <c r="F11">
-        <v>6.81345</v>
+        <v>7.570499999999999</v>
       </c>
       <c r="G11">
         <v>2.11</v>
@@ -2177,28 +2177,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M11">
-        <v>0.3427165349999999</v>
+        <v>0.3807961499999999</v>
       </c>
       <c r="N11">
-        <v>8.037283465000002</v>
+        <v>7.999203850000001</v>
       </c>
       <c r="O11">
-        <v>2.00932086625</v>
+        <v>1.9998009625</v>
       </c>
       <c r="P11">
-        <v>6.027962598750001</v>
+        <v>5.999402887500001</v>
       </c>
       <c r="Q11">
-        <v>6.627962598750001</v>
+        <v>6.5994028875</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1962115672837019</v>
+        <v>0.1974938483347139</v>
       </c>
       <c r="T11">
-        <v>1.454594812546301</v>
+        <v>1.466995450334419</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.45169445938756</v>
+        <v>22.0065250134488</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1815169635012425</v>
+        <v>0.1810861507743163</v>
       </c>
       <c r="C12">
-        <v>70.46763779815394</v>
+        <v>69.95237757418077</v>
       </c>
       <c r="D12">
-        <v>75.92813779815394</v>
+        <v>76.16992757418078</v>
       </c>
       <c r="E12">
-        <v>7.4655</v>
+        <v>8.22255</v>
       </c>
       <c r="F12">
-        <v>7.5705</v>
+        <v>8.32755</v>
       </c>
       <c r="G12">
         <v>2.11</v>
@@ -2259,28 +2259,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M12">
-        <v>0.38079615</v>
+        <v>0.418875765</v>
       </c>
       <c r="N12">
-        <v>7.999203850000001</v>
+        <v>7.961124235000001</v>
       </c>
       <c r="O12">
-        <v>1.9998009625</v>
+        <v>1.99028105875</v>
       </c>
       <c r="P12">
-        <v>5.999402887500001</v>
+        <v>5.970843176250001</v>
       </c>
       <c r="Q12">
-        <v>6.5994028875</v>
+        <v>6.57084317625</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1974938483347139</v>
+        <v>0.198804944690243</v>
       </c>
       <c r="T12">
-        <v>1.466995450334419</v>
+        <v>1.479674754140248</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.0065250134488</v>
+        <v>20.005931830408</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1810861507743163</v>
+        <v>0.18065533804739</v>
       </c>
       <c r="C13">
-        <v>69.95237757418077</v>
+        <v>69.4386622073006</v>
       </c>
       <c r="D13">
-        <v>76.16992757418078</v>
+        <v>76.41326220730059</v>
       </c>
       <c r="E13">
-        <v>8.22255</v>
+        <v>8.9796</v>
       </c>
       <c r="F13">
-        <v>8.32755</v>
+        <v>9.0846</v>
       </c>
       <c r="G13">
         <v>2.11</v>
@@ -2341,28 +2341,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M13">
-        <v>0.418875765</v>
+        <v>0.45695538</v>
       </c>
       <c r="N13">
-        <v>7.961124235000001</v>
+        <v>7.923044620000001</v>
       </c>
       <c r="O13">
-        <v>1.99028105875</v>
+        <v>1.980761155</v>
       </c>
       <c r="P13">
-        <v>5.970843176250001</v>
+        <v>5.942283465000001</v>
       </c>
       <c r="Q13">
-        <v>6.57084317625</v>
+        <v>6.542283465000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.198804944690243</v>
+        <v>0.2001458386902158</v>
       </c>
       <c r="T13">
-        <v>1.479674754140248</v>
+        <v>1.492642223941664</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.005931830408</v>
+        <v>18.33877084454067</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.18065533804739</v>
+        <v>0.1802245253204637</v>
       </c>
       <c r="C14">
-        <v>69.4386622073006</v>
+        <v>68.92650655069797</v>
       </c>
       <c r="D14">
-        <v>76.41326220730059</v>
+        <v>76.65815655069797</v>
       </c>
       <c r="E14">
-        <v>8.9796</v>
+        <v>9.736649999999999</v>
       </c>
       <c r="F14">
-        <v>9.0846</v>
+        <v>9.84165</v>
       </c>
       <c r="G14">
         <v>2.11</v>
@@ -2423,28 +2423,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M14">
-        <v>0.45695538</v>
+        <v>0.495034995</v>
       </c>
       <c r="N14">
-        <v>7.923044620000001</v>
+        <v>7.884965005000001</v>
       </c>
       <c r="O14">
-        <v>1.980761155</v>
+        <v>1.97124125125</v>
       </c>
       <c r="P14">
-        <v>5.942283465000001</v>
+        <v>5.91372375375</v>
       </c>
       <c r="Q14">
-        <v>6.542283465000001</v>
+        <v>6.51372375375</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2001458386902158</v>
+        <v>0.2015175578396134</v>
       </c>
       <c r="T14">
-        <v>1.492642223941664</v>
+        <v>1.505907796497136</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.33877084454067</v>
+        <v>16.92809616419138</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1802245253204637</v>
+        <v>0.1797937125935374</v>
       </c>
       <c r="C15">
-        <v>68.92650655069797</v>
+        <v>68.41592564857964</v>
       </c>
       <c r="D15">
-        <v>76.65815655069797</v>
+        <v>76.90462564857965</v>
       </c>
       <c r="E15">
-        <v>9.736649999999999</v>
+        <v>10.4937</v>
       </c>
       <c r="F15">
-        <v>9.84165</v>
+        <v>10.5987</v>
       </c>
       <c r="G15">
         <v>2.11</v>
@@ -2505,28 +2505,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M15">
-        <v>0.495034995</v>
+        <v>0.53311461</v>
       </c>
       <c r="N15">
-        <v>7.884965005000001</v>
+        <v>7.846885390000001</v>
       </c>
       <c r="O15">
-        <v>1.97124125125</v>
+        <v>1.9617213475</v>
       </c>
       <c r="P15">
-        <v>5.91372375375</v>
+        <v>5.8851640425</v>
       </c>
       <c r="Q15">
-        <v>6.51372375375</v>
+        <v>6.4851640425</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2015175578396134</v>
+        <v>0.2029211774343459</v>
       </c>
       <c r="T15">
-        <v>1.505907796497136</v>
+        <v>1.519481870739944</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.92809616419138</v>
+        <v>15.71894643817771</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1797937125935374</v>
+        <v>0.1793628998666112</v>
       </c>
       <c r="C16">
-        <v>68.41592564857964</v>
+        <v>67.90693473925526</v>
       </c>
       <c r="D16">
-        <v>76.90462564857965</v>
+        <v>77.15268473925526</v>
       </c>
       <c r="E16">
-        <v>10.4937</v>
+        <v>11.25075</v>
       </c>
       <c r="F16">
-        <v>10.5987</v>
+        <v>11.35575</v>
       </c>
       <c r="G16">
         <v>2.11</v>
@@ -2587,28 +2587,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M16">
-        <v>0.53311461</v>
+        <v>0.5711942250000001</v>
       </c>
       <c r="N16">
-        <v>7.846885390000001</v>
+        <v>7.808805775000001</v>
       </c>
       <c r="O16">
-        <v>1.9617213475</v>
+        <v>1.95220144375</v>
       </c>
       <c r="P16">
-        <v>5.8851640425</v>
+        <v>5.856604331250001</v>
       </c>
       <c r="Q16">
-        <v>6.4851640425</v>
+        <v>6.45660433125</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2029211774343459</v>
+        <v>0.2043578233724837</v>
       </c>
       <c r="T16">
-        <v>1.519481870739944</v>
+        <v>1.533375334964936</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.71894643817771</v>
+        <v>14.67101667563253</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1793628998666112</v>
+        <v>0.1789320871396849</v>
       </c>
       <c r="C17">
-        <v>67.90693473925526</v>
+        <v>67.39954925827783</v>
       </c>
       <c r="D17">
-        <v>77.15268473925526</v>
+        <v>77.40234925827784</v>
       </c>
       <c r="E17">
-        <v>11.25075</v>
+        <v>12.0078</v>
       </c>
       <c r="F17">
-        <v>11.35575</v>
+        <v>12.1128</v>
       </c>
       <c r="G17">
         <v>2.11</v>
@@ -2669,28 +2669,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M17">
-        <v>0.5711942249999999</v>
+        <v>0.60927384</v>
       </c>
       <c r="N17">
-        <v>7.808805775000001</v>
+        <v>7.770726160000001</v>
       </c>
       <c r="O17">
-        <v>1.95220144375</v>
+        <v>1.94268154</v>
       </c>
       <c r="P17">
-        <v>5.856604331250001</v>
+        <v>5.82804462</v>
       </c>
       <c r="Q17">
-        <v>6.45660433125</v>
+        <v>6.42804462</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2043578233724837</v>
+        <v>0.2058286751662916</v>
       </c>
       <c r="T17">
-        <v>1.533375334964936</v>
+        <v>1.54759959595719</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.67101667563253</v>
+        <v>13.7540781334055</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1789320871396849</v>
+        <v>0.1785012744127587</v>
       </c>
       <c r="C18">
-        <v>67.39954925827783</v>
+        <v>66.89378484164558</v>
       </c>
       <c r="D18">
-        <v>77.40234925827784</v>
+        <v>77.65363484164558</v>
       </c>
       <c r="E18">
-        <v>12.0078</v>
+        <v>12.76485</v>
       </c>
       <c r="F18">
-        <v>12.1128</v>
+        <v>12.86985</v>
       </c>
       <c r="G18">
         <v>2.11</v>
@@ -2751,28 +2751,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M18">
-        <v>0.60927384</v>
+        <v>0.6473534550000001</v>
       </c>
       <c r="N18">
-        <v>7.770726160000001</v>
+        <v>7.732646545000001</v>
       </c>
       <c r="O18">
-        <v>1.94268154</v>
+        <v>1.93316163625</v>
       </c>
       <c r="P18">
-        <v>5.82804462</v>
+        <v>5.79948490875</v>
       </c>
       <c r="Q18">
-        <v>6.42804462</v>
+        <v>6.39948490875</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2058286751662916</v>
+        <v>0.2073349691719984</v>
       </c>
       <c r="T18">
-        <v>1.54759959595719</v>
+        <v>1.562166610226365</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.7540781334055</v>
+        <v>12.94501471379341</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1785012744127587</v>
+        <v>0.1782729616858324</v>
       </c>
       <c r="C19">
-        <v>66.89378484164558</v>
+        <v>66.27056828886992</v>
       </c>
       <c r="D19">
-        <v>77.65363484164558</v>
+        <v>77.78746828886993</v>
       </c>
       <c r="E19">
-        <v>12.76485</v>
+        <v>13.5219</v>
       </c>
       <c r="F19">
-        <v>12.86985</v>
+        <v>13.6269</v>
       </c>
       <c r="G19">
         <v>2.11</v>
@@ -2833,45 +2833,45 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M19">
-        <v>0.6473534550000001</v>
+        <v>0.7058734200000001</v>
       </c>
       <c r="N19">
-        <v>7.732646545000001</v>
+        <v>7.674126580000001</v>
       </c>
       <c r="O19">
-        <v>1.93316163625</v>
+        <v>1.918531645</v>
       </c>
       <c r="P19">
-        <v>5.79948490875</v>
+        <v>5.755594935000001</v>
       </c>
       <c r="Q19">
-        <v>6.39948490875</v>
+        <v>6.355594935000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2073349691719984</v>
+        <v>0.2088780020558932</v>
       </c>
       <c r="T19">
-        <v>1.562166610226365</v>
+        <v>1.577088917526496</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>12.94501471379341</v>
+        <v>11.87181690450959</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1782729616858324</v>
+        <v>0.1778533989589062</v>
       </c>
       <c r="C20">
-        <v>66.27056828886992</v>
+        <v>65.76066620458639</v>
       </c>
       <c r="D20">
-        <v>77.78746828886992</v>
+        <v>78.03461620458638</v>
       </c>
       <c r="E20">
-        <v>13.5219</v>
+        <v>14.27895</v>
       </c>
       <c r="F20">
-        <v>13.6269</v>
+        <v>14.38395</v>
       </c>
       <c r="G20">
         <v>2.11</v>
@@ -2915,28 +2915,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M20">
-        <v>0.70587342</v>
+        <v>0.74508861</v>
       </c>
       <c r="N20">
-        <v>7.674126580000001</v>
+        <v>7.634911390000001</v>
       </c>
       <c r="O20">
-        <v>1.918531645</v>
+        <v>1.9087278475</v>
       </c>
       <c r="P20">
-        <v>5.755594935000001</v>
+        <v>5.726183542500001</v>
       </c>
       <c r="Q20">
-        <v>6.355594935000001</v>
+        <v>6.326183542500001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2088780020558932</v>
+        <v>0.2104591345171681</v>
       </c>
       <c r="T20">
-        <v>1.577088917526496</v>
+        <v>1.592379676858729</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.8718169045096</v>
+        <v>11.24698443585119</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1778533989589062</v>
+        <v>0.1774338362319799</v>
       </c>
       <c r="C21">
-        <v>65.76066620458639</v>
+        <v>65.25233961269053</v>
       </c>
       <c r="D21">
-        <v>78.03461620458638</v>
+        <v>78.28333961269054</v>
       </c>
       <c r="E21">
-        <v>14.27895</v>
+        <v>15.036</v>
       </c>
       <c r="F21">
-        <v>14.38395</v>
+        <v>15.141</v>
       </c>
       <c r="G21">
         <v>2.11</v>
@@ -2997,28 +2997,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M21">
-        <v>0.74508861</v>
+        <v>0.7843038</v>
       </c>
       <c r="N21">
-        <v>7.634911390000001</v>
+        <v>7.595696200000001</v>
       </c>
       <c r="O21">
-        <v>1.9087278475</v>
+        <v>1.89892405</v>
       </c>
       <c r="P21">
-        <v>5.726183542500001</v>
+        <v>5.696772150000001</v>
       </c>
       <c r="Q21">
-        <v>6.326183542500001</v>
+        <v>6.296772150000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2104591345171681</v>
+        <v>0.2120797952899748</v>
       </c>
       <c r="T21">
-        <v>1.592379676858729</v>
+        <v>1.608052705174267</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.24698443585119</v>
+        <v>10.68463521405864</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1774338362319799</v>
+        <v>0.1770142735050536</v>
       </c>
       <c r="C22">
-        <v>65.25233961269053</v>
+        <v>64.74560362627633</v>
       </c>
       <c r="D22">
-        <v>78.28333961269054</v>
+        <v>78.53365362627633</v>
       </c>
       <c r="E22">
-        <v>15.036</v>
+        <v>15.79305</v>
       </c>
       <c r="F22">
-        <v>15.141</v>
+        <v>15.89805</v>
       </c>
       <c r="G22">
         <v>2.11</v>
@@ -3079,28 +3079,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M22">
-        <v>0.7843038</v>
+        <v>0.8235189900000001</v>
       </c>
       <c r="N22">
-        <v>7.595696200000001</v>
+        <v>7.556481010000001</v>
       </c>
       <c r="O22">
-        <v>1.89892405</v>
+        <v>1.8891202525</v>
       </c>
       <c r="P22">
-        <v>5.696772150000001</v>
+        <v>5.667360757500001</v>
       </c>
       <c r="Q22">
-        <v>6.296772150000001</v>
+        <v>6.267360757500001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2120797952899748</v>
+        <v>0.2137414854494349</v>
       </c>
       <c r="T22">
-        <v>1.608052705174267</v>
+        <v>1.624122519016782</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.68463521405864</v>
+        <v>10.17584306100822</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1770142735050536</v>
+        <v>0.1768752107781273</v>
       </c>
       <c r="C23">
-        <v>64.74560362627633</v>
+        <v>64.07187299661281</v>
       </c>
       <c r="D23">
-        <v>78.53365362627633</v>
+        <v>78.61697299661282</v>
       </c>
       <c r="E23">
-        <v>15.79305</v>
+        <v>16.5501</v>
       </c>
       <c r="F23">
-        <v>15.89805</v>
+        <v>16.6551</v>
       </c>
       <c r="G23">
         <v>2.11</v>
@@ -3161,45 +3161,45 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M23">
-        <v>0.82351899</v>
+        <v>0.8910478500000001</v>
       </c>
       <c r="N23">
-        <v>7.556481010000001</v>
+        <v>7.488952150000001</v>
       </c>
       <c r="O23">
-        <v>1.8891202525</v>
+        <v>1.8722380375</v>
       </c>
       <c r="P23">
-        <v>5.667360757500001</v>
+        <v>5.6167141125</v>
       </c>
       <c r="Q23">
-        <v>6.267360757500001</v>
+        <v>6.2167141125</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2137414854494349</v>
+        <v>0.2154457830488812</v>
       </c>
       <c r="T23">
-        <v>1.624122519016782</v>
+        <v>1.640604379368078</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.17584306100822</v>
+        <v>9.404657673546938</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1768752107781273</v>
+        <v>0.1764683980512011</v>
       </c>
       <c r="C24">
-        <v>64.07187299661281</v>
+        <v>63.55958290523974</v>
       </c>
       <c r="D24">
-        <v>78.61697299661282</v>
+        <v>78.86173290523973</v>
       </c>
       <c r="E24">
-        <v>16.5501</v>
+        <v>17.30715</v>
       </c>
       <c r="F24">
-        <v>16.6551</v>
+        <v>17.41215</v>
       </c>
       <c r="G24">
         <v>2.11</v>
@@ -3243,28 +3243,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M24">
-        <v>0.8910478500000001</v>
+        <v>0.9315500250000001</v>
       </c>
       <c r="N24">
-        <v>7.488952150000001</v>
+        <v>7.448449975000001</v>
       </c>
       <c r="O24">
-        <v>1.8722380375</v>
+        <v>1.86211249375</v>
       </c>
       <c r="P24">
-        <v>5.6167141125</v>
+        <v>5.58633748125</v>
       </c>
       <c r="Q24">
-        <v>6.2167141125</v>
+        <v>6.18633748125</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2154457830488812</v>
+        <v>0.2171943481184429</v>
       </c>
       <c r="T24">
-        <v>1.640604379368078</v>
+        <v>1.65751433998824</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.404657673546938</v>
+        <v>8.995759513827505</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1764683980512011</v>
+        <v>0.1760615853242748</v>
       </c>
       <c r="C25">
-        <v>63.55958290523974</v>
+        <v>63.04882160603704</v>
       </c>
       <c r="D25">
-        <v>78.86173290523973</v>
+        <v>79.10802160603704</v>
       </c>
       <c r="E25">
-        <v>17.30715</v>
+        <v>18.0642</v>
       </c>
       <c r="F25">
-        <v>17.41215</v>
+        <v>18.1692</v>
       </c>
       <c r="G25">
         <v>2.11</v>
@@ -3325,28 +3325,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M25">
-        <v>0.9315500250000001</v>
+        <v>0.9720522</v>
       </c>
       <c r="N25">
-        <v>7.448449975000001</v>
+        <v>7.407947800000001</v>
       </c>
       <c r="O25">
-        <v>1.86211249375</v>
+        <v>1.85198695</v>
       </c>
       <c r="P25">
-        <v>5.58633748125</v>
+        <v>5.55596085</v>
       </c>
       <c r="Q25">
-        <v>6.18633748125</v>
+        <v>6.15596085</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2171943481184429</v>
+        <v>0.2189889280582563</v>
       </c>
       <c r="T25">
-        <v>1.65751433998824</v>
+        <v>1.67486929957209</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.995759513827505</v>
+        <v>8.620936200751359</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1760615853242748</v>
+        <v>0.1756547725973485</v>
       </c>
       <c r="C26">
-        <v>63.04882160603704</v>
+        <v>62.53960346733554</v>
       </c>
       <c r="D26">
-        <v>79.10802160603704</v>
+        <v>79.35585346733554</v>
       </c>
       <c r="E26">
-        <v>18.0642</v>
+        <v>18.82125</v>
       </c>
       <c r="F26">
-        <v>18.1692</v>
+        <v>18.92625</v>
       </c>
       <c r="G26">
         <v>2.11</v>
@@ -3407,28 +3407,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M26">
-        <v>0.9720522</v>
+        <v>1.012554375</v>
       </c>
       <c r="N26">
-        <v>7.407947800000001</v>
+        <v>7.367445625000001</v>
       </c>
       <c r="O26">
-        <v>1.85198695</v>
+        <v>1.84186140625</v>
       </c>
       <c r="P26">
-        <v>5.55596085</v>
+        <v>5.525584218750001</v>
       </c>
       <c r="Q26">
-        <v>6.15596085</v>
+        <v>6.12558421875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2189889280582563</v>
+        <v>0.2208313634631314</v>
       </c>
       <c r="T26">
-        <v>1.67486929957209</v>
+        <v>1.692687058078176</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.620936200751359</v>
+        <v>8.276098752721307</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1756547725973485</v>
+        <v>0.1752479598704223</v>
       </c>
       <c r="C27">
-        <v>62.53960346733554</v>
+        <v>62.03194303808597</v>
       </c>
       <c r="D27">
-        <v>79.35585346733554</v>
+        <v>79.60524303808597</v>
       </c>
       <c r="E27">
-        <v>18.82125</v>
+        <v>19.5783</v>
       </c>
       <c r="F27">
-        <v>18.92625</v>
+        <v>19.6833</v>
       </c>
       <c r="G27">
         <v>2.11</v>
@@ -3489,28 +3489,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M27">
-        <v>1.012554375</v>
+        <v>1.05305655</v>
       </c>
       <c r="N27">
-        <v>7.367445625000001</v>
+        <v>7.326943450000001</v>
       </c>
       <c r="O27">
-        <v>1.84186140625</v>
+        <v>1.8317358625</v>
       </c>
       <c r="P27">
-        <v>5.525584218750001</v>
+        <v>5.4952075875</v>
       </c>
       <c r="Q27">
-        <v>6.12558421875</v>
+        <v>6.0952075875</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2208313634631314</v>
+        <v>0.2227235944194896</v>
       </c>
       <c r="T27">
-        <v>1.692687058078176</v>
+        <v>1.710986377624967</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.276098752721307</v>
+        <v>7.957787262232024</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1752479598704223</v>
+        <v>0.174841147143496</v>
       </c>
       <c r="C28">
-        <v>62.03194303808597</v>
+        <v>61.52585505070619</v>
       </c>
       <c r="D28">
-        <v>79.60524303808597</v>
+        <v>79.85620505070619</v>
       </c>
       <c r="E28">
-        <v>19.5783</v>
+        <v>20.33535</v>
       </c>
       <c r="F28">
-        <v>19.6833</v>
+        <v>20.44035</v>
       </c>
       <c r="G28">
         <v>2.11</v>
@@ -3571,28 +3571,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M28">
-        <v>1.05305655</v>
+        <v>1.093558725</v>
       </c>
       <c r="N28">
-        <v>7.326943450000001</v>
+        <v>7.286441275</v>
       </c>
       <c r="O28">
-        <v>1.8317358625</v>
+        <v>1.82161031875</v>
       </c>
       <c r="P28">
-        <v>5.4952075875</v>
+        <v>5.46483095625</v>
       </c>
       <c r="Q28">
-        <v>6.0952075875</v>
+        <v>6.06483095625</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2227235944194896</v>
+        <v>0.2246676673198576</v>
       </c>
       <c r="T28">
-        <v>1.710986377624967</v>
+        <v>1.729787048392218</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.957787262232024</v>
+        <v>7.663054400667875</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.174841147143496</v>
+        <v>0.1746023344165697</v>
       </c>
       <c r="C29">
-        <v>61.52585505070619</v>
+        <v>60.91686663807204</v>
       </c>
       <c r="D29">
-        <v>79.85620505070619</v>
+        <v>80.00426663807204</v>
       </c>
       <c r="E29">
-        <v>20.33535</v>
+        <v>21.0924</v>
       </c>
       <c r="F29">
-        <v>20.44035</v>
+        <v>21.1974</v>
       </c>
       <c r="G29">
         <v>2.11</v>
@@ -3653,45 +3653,45 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M29">
-        <v>1.093558725</v>
+        <v>1.15101882</v>
       </c>
       <c r="N29">
-        <v>7.286441275</v>
+        <v>7.228981180000001</v>
       </c>
       <c r="O29">
-        <v>1.82161031875</v>
+        <v>1.807245295</v>
       </c>
       <c r="P29">
-        <v>5.46483095625</v>
+        <v>5.421735885</v>
       </c>
       <c r="Q29">
-        <v>6.06483095625</v>
+        <v>6.021735885</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2246676673198576</v>
+        <v>0.2266657422452358</v>
       </c>
       <c r="T29">
-        <v>1.729787048392218</v>
+        <v>1.749109960014115</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.663054400667875</v>
+        <v>7.280506499450634</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1746023344165697</v>
+        <v>0.1742015216896435</v>
       </c>
       <c r="C30">
-        <v>60.91686663807204</v>
+        <v>60.40955455281772</v>
       </c>
       <c r="D30">
-        <v>80.00426663807204</v>
+        <v>80.25400455281772</v>
       </c>
       <c r="E30">
-        <v>21.0924</v>
+        <v>21.84945</v>
       </c>
       <c r="F30">
-        <v>21.1974</v>
+        <v>21.95445</v>
       </c>
       <c r="G30">
         <v>2.11</v>
@@ -3735,28 +3735,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M30">
-        <v>1.15101882</v>
+        <v>1.192126635</v>
       </c>
       <c r="N30">
-        <v>7.228981180000001</v>
+        <v>7.187873365000001</v>
       </c>
       <c r="O30">
-        <v>1.807245295</v>
+        <v>1.79696834125</v>
       </c>
       <c r="P30">
-        <v>5.421735885</v>
+        <v>5.39090502375</v>
       </c>
       <c r="Q30">
-        <v>6.021735885</v>
+        <v>5.99090502375</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2266657422452358</v>
+        <v>0.2287201009713288</v>
       </c>
       <c r="T30">
-        <v>1.749109960014115</v>
+        <v>1.768977179005643</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.280506499450634</v>
+        <v>7.029454551193716</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1742015216896435</v>
+        <v>0.1738007089627172</v>
       </c>
       <c r="C31">
-        <v>60.40955455281772</v>
+        <v>59.90380649225412</v>
       </c>
       <c r="D31">
-        <v>80.25400455281772</v>
+        <v>80.50530649225412</v>
       </c>
       <c r="E31">
-        <v>21.84945</v>
+        <v>22.6065</v>
       </c>
       <c r="F31">
-        <v>21.95445</v>
+        <v>22.7115</v>
       </c>
       <c r="G31">
         <v>2.11</v>
@@ -3817,28 +3817,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M31">
-        <v>1.192126635</v>
+        <v>1.23323445</v>
       </c>
       <c r="N31">
-        <v>7.187873365000001</v>
+        <v>7.146765550000001</v>
       </c>
       <c r="O31">
-        <v>1.79696834125</v>
+        <v>1.7866913875</v>
       </c>
       <c r="P31">
-        <v>5.39090502375</v>
+        <v>5.360074162500001</v>
       </c>
       <c r="Q31">
-        <v>5.99090502375</v>
+        <v>5.960074162500001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2287201009713288</v>
+        <v>0.2308331556610246</v>
       </c>
       <c r="T31">
-        <v>1.768977179005643</v>
+        <v>1.7894120328255</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.029454551193717</v>
+        <v>6.795139399487261</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1738007089627172</v>
+        <v>0.1733998962357909</v>
       </c>
       <c r="C32">
-        <v>59.90380649225412</v>
+        <v>59.39963719497482</v>
       </c>
       <c r="D32">
-        <v>80.50530649225412</v>
+        <v>80.75818719497482</v>
       </c>
       <c r="E32">
-        <v>22.6065</v>
+        <v>23.36355</v>
       </c>
       <c r="F32">
-        <v>22.7115</v>
+        <v>23.46855</v>
       </c>
       <c r="G32">
         <v>2.11</v>
@@ -3899,28 +3899,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M32">
-        <v>1.23323445</v>
+        <v>1.274342265</v>
       </c>
       <c r="N32">
-        <v>7.146765550000001</v>
+        <v>7.105657735000001</v>
       </c>
       <c r="O32">
-        <v>1.7866913875</v>
+        <v>1.77641443375</v>
       </c>
       <c r="P32">
-        <v>5.360074162500001</v>
+        <v>5.329243301250001</v>
       </c>
       <c r="Q32">
-        <v>5.960074162500001</v>
+        <v>5.929243301250001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2308331556610246</v>
+        <v>0.2330074583127405</v>
       </c>
       <c r="T32">
-        <v>1.7894120328255</v>
+        <v>1.810439201248832</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.795139399487261</v>
+        <v>6.575941354342509</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1733998962357909</v>
+        <v>0.1729990835088647</v>
       </c>
       <c r="C33">
-        <v>59.39963719497482</v>
+        <v>58.89706158534244</v>
       </c>
       <c r="D33">
-        <v>80.75818719497482</v>
+        <v>81.01266158534244</v>
       </c>
       <c r="E33">
-        <v>23.36355</v>
+        <v>24.1206</v>
       </c>
       <c r="F33">
-        <v>23.46855</v>
+        <v>24.2256</v>
       </c>
       <c r="G33">
         <v>2.11</v>
@@ -3981,28 +3981,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M33">
-        <v>1.274342265</v>
+        <v>1.31545008</v>
       </c>
       <c r="N33">
-        <v>7.105657735000001</v>
+        <v>7.064549920000001</v>
       </c>
       <c r="O33">
-        <v>1.77641443375</v>
+        <v>1.76613748</v>
       </c>
       <c r="P33">
-        <v>5.329243301250001</v>
+        <v>5.298412440000001</v>
       </c>
       <c r="Q33">
-        <v>5.929243301250001</v>
+        <v>5.89841244</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2330074583127405</v>
+        <v>0.2352457110424481</v>
       </c>
       <c r="T33">
-        <v>1.810439201248832</v>
+        <v>1.832084815802261</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.575941354342509</v>
+        <v>6.370443187019307</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1729990835088647</v>
+        <v>0.1725982707819385</v>
       </c>
       <c r="C34">
-        <v>58.89706158534244</v>
+        <v>58.39609477642488</v>
       </c>
       <c r="D34">
-        <v>81.01266158534244</v>
+        <v>81.26874477642488</v>
       </c>
       <c r="E34">
-        <v>24.1206</v>
+        <v>24.87765</v>
       </c>
       <c r="F34">
-        <v>24.2256</v>
+        <v>24.98265</v>
       </c>
       <c r="G34">
         <v>2.11</v>
@@ -4063,28 +4063,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M34">
-        <v>1.31545008</v>
+        <v>1.356557895</v>
       </c>
       <c r="N34">
-        <v>7.064549920000001</v>
+        <v>7.023442105000001</v>
       </c>
       <c r="O34">
-        <v>1.76613748</v>
+        <v>1.75586052625</v>
       </c>
       <c r="P34">
-        <v>5.298412440000001</v>
+        <v>5.267581578750001</v>
       </c>
       <c r="Q34">
-        <v>5.89841244</v>
+        <v>5.86758157875</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2352457110424481</v>
+        <v>0.2375507772864753</v>
       </c>
       <c r="T34">
-        <v>1.832084815802261</v>
+        <v>1.854376568103554</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.370443187019307</v>
+        <v>6.177399454079327</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1725982707819385</v>
+        <v>0.1724524580550122</v>
       </c>
       <c r="C35">
-        <v>58.39609477642488</v>
+        <v>57.732608039797</v>
       </c>
       <c r="D35">
-        <v>81.26874477642488</v>
+        <v>81.362308039797</v>
       </c>
       <c r="E35">
-        <v>24.87765</v>
+        <v>25.6347</v>
       </c>
       <c r="F35">
-        <v>24.98265</v>
+        <v>25.7397</v>
       </c>
       <c r="G35">
         <v>2.11</v>
@@ -4145,45 +4145,45 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M35">
-        <v>1.356557895</v>
+        <v>1.42340541</v>
       </c>
       <c r="N35">
-        <v>7.023442105000001</v>
+        <v>6.956594590000001</v>
       </c>
       <c r="O35">
-        <v>1.75586052625</v>
+        <v>1.7391486475</v>
       </c>
       <c r="P35">
-        <v>5.267581578750001</v>
+        <v>5.2174459425</v>
       </c>
       <c r="Q35">
-        <v>5.86758157875</v>
+        <v>5.8174459425</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2375507772864753</v>
+        <v>0.2399256940227457</v>
       </c>
       <c r="T35">
-        <v>1.854376568103554</v>
+        <v>1.877343828050341</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.177399454079327</v>
+        <v>5.887289693524489</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1724524580550122</v>
+        <v>0.1720591453280859</v>
       </c>
       <c r="C36">
-        <v>57.732608039797</v>
+        <v>57.22901161071253</v>
       </c>
       <c r="D36">
-        <v>81.362308039797</v>
+        <v>81.61576161071254</v>
       </c>
       <c r="E36">
-        <v>25.6347</v>
+        <v>26.39175</v>
       </c>
       <c r="F36">
-        <v>25.7397</v>
+        <v>26.49675</v>
       </c>
       <c r="G36">
         <v>2.11</v>
@@ -4227,28 +4227,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M36">
-        <v>1.42340541</v>
+        <v>1.465270275</v>
       </c>
       <c r="N36">
-        <v>6.956594590000001</v>
+        <v>6.914729725000001</v>
       </c>
       <c r="O36">
-        <v>1.7391486475</v>
+        <v>1.72868243125</v>
       </c>
       <c r="P36">
-        <v>5.2174459425</v>
+        <v>5.186047293750001</v>
       </c>
       <c r="Q36">
-        <v>5.8174459425</v>
+        <v>5.78604729375</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2399256940227457</v>
+        <v>0.2423736851201322</v>
       </c>
       <c r="T36">
-        <v>1.877343828050341</v>
+        <v>1.901017772918567</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.887289693524489</v>
+        <v>5.719081416566647</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1720591453280859</v>
+        <v>0.1716658326011596</v>
       </c>
       <c r="C37">
-        <v>57.22901161071253</v>
+        <v>56.726999193954</v>
       </c>
       <c r="D37">
-        <v>81.61576161071254</v>
+        <v>81.870799193954</v>
       </c>
       <c r="E37">
-        <v>26.39175</v>
+        <v>27.1488</v>
       </c>
       <c r="F37">
-        <v>26.49675</v>
+        <v>27.2538</v>
       </c>
       <c r="G37">
         <v>2.11</v>
@@ -4309,28 +4309,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M37">
-        <v>1.465270275</v>
+        <v>1.50713514</v>
       </c>
       <c r="N37">
-        <v>6.914729725000001</v>
+        <v>6.872864860000001</v>
       </c>
       <c r="O37">
-        <v>1.72868243125</v>
+        <v>1.718216215</v>
       </c>
       <c r="P37">
-        <v>5.186047293750001</v>
+        <v>5.154648645000001</v>
       </c>
       <c r="Q37">
-        <v>5.78604729375</v>
+        <v>5.754648645000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2423736851201322</v>
+        <v>0.244898175939312</v>
       </c>
       <c r="T37">
-        <v>1.901017772918567</v>
+        <v>1.925431528563925</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.719081416566647</v>
+        <v>5.56021804388424</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1716658326011597</v>
+        <v>0.1712725198742334</v>
       </c>
       <c r="C38">
-        <v>56.72699919395399</v>
+        <v>56.22658568550515</v>
       </c>
       <c r="D38">
-        <v>81.87079919395399</v>
+        <v>82.12743568550515</v>
       </c>
       <c r="E38">
-        <v>27.1488</v>
+        <v>27.90585</v>
       </c>
       <c r="F38">
-        <v>27.2538</v>
+        <v>28.01085</v>
       </c>
       <c r="G38">
         <v>2.11</v>
@@ -4391,28 +4391,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M38">
-        <v>1.50713514</v>
+        <v>1.549000005</v>
       </c>
       <c r="N38">
-        <v>6.872864860000001</v>
+        <v>6.830999995000001</v>
       </c>
       <c r="O38">
-        <v>1.718216215</v>
+        <v>1.70774999875</v>
       </c>
       <c r="P38">
-        <v>5.154648645000001</v>
+        <v>5.123249996250001</v>
       </c>
       <c r="Q38">
-        <v>5.754648645000001</v>
+        <v>5.723249996250001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.244898175939312</v>
+        <v>0.24750280932418</v>
       </c>
       <c r="T38">
-        <v>1.925431528563925</v>
+        <v>1.950620324071041</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.560218043884241</v>
+        <v>5.409941880536018</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1712725198742334</v>
+        <v>0.1708792071473071</v>
       </c>
       <c r="C39">
-        <v>56.22658568550515</v>
+        <v>55.72778616871204</v>
       </c>
       <c r="D39">
-        <v>82.12743568550515</v>
+        <v>82.38568616871204</v>
       </c>
       <c r="E39">
-        <v>27.90585</v>
+        <v>28.6629</v>
       </c>
       <c r="F39">
-        <v>28.01085</v>
+        <v>28.7679</v>
       </c>
       <c r="G39">
         <v>2.11</v>
@@ -4473,28 +4473,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M39">
-        <v>1.549000005</v>
+        <v>1.59086487</v>
       </c>
       <c r="N39">
-        <v>6.830999995000001</v>
+        <v>6.789135130000001</v>
       </c>
       <c r="O39">
-        <v>1.70774999875</v>
+        <v>1.6972837825</v>
       </c>
       <c r="P39">
-        <v>5.123249996250001</v>
+        <v>5.0918513475</v>
       </c>
       <c r="Q39">
-        <v>5.723249996250001</v>
+        <v>5.6918513475</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.24750280932418</v>
+        <v>0.2501914631408179</v>
       </c>
       <c r="T39">
-        <v>1.950620324071041</v>
+        <v>1.976621661368709</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.409941880536018</v>
+        <v>5.267574988942965</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1708792071473071</v>
+        <v>0.1704858944203808</v>
       </c>
       <c r="C40">
-        <v>55.72778616871204</v>
+        <v>55.23061591723805</v>
       </c>
       <c r="D40">
-        <v>82.38568616871204</v>
+        <v>82.64556591723806</v>
       </c>
       <c r="E40">
-        <v>28.6629</v>
+        <v>29.41995</v>
       </c>
       <c r="F40">
-        <v>28.7679</v>
+        <v>29.52495</v>
       </c>
       <c r="G40">
         <v>2.11</v>
@@ -4555,28 +4555,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M40">
-        <v>1.59086487</v>
+        <v>1.632729735</v>
       </c>
       <c r="N40">
-        <v>6.789135130000001</v>
+        <v>6.747270265000001</v>
       </c>
       <c r="O40">
-        <v>1.6972837825</v>
+        <v>1.68681756625</v>
       </c>
       <c r="P40">
-        <v>5.0918513475</v>
+        <v>5.060452698750001</v>
       </c>
       <c r="Q40">
-        <v>5.6918513475</v>
+        <v>5.66045269875</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2501914631408179</v>
+        <v>0.2529682695416079</v>
       </c>
       <c r="T40">
-        <v>1.976621661368709</v>
+        <v>2.003475501528595</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.267574988942965</v>
+        <v>5.132508963585453</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1704858944203808</v>
+        <v>0.1700925816934546</v>
       </c>
       <c r="C41">
-        <v>55.23061591723805</v>
+        <v>54.73509039807504</v>
       </c>
       <c r="D41">
-        <v>82.64556591723806</v>
+        <v>82.90709039807504</v>
       </c>
       <c r="E41">
-        <v>29.41995</v>
+        <v>30.177</v>
       </c>
       <c r="F41">
-        <v>29.52495</v>
+        <v>30.282</v>
       </c>
       <c r="G41">
         <v>2.11</v>
@@ -4637,28 +4637,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M41">
-        <v>1.632729735</v>
+        <v>1.6745946</v>
       </c>
       <c r="N41">
-        <v>6.747270265000001</v>
+        <v>6.705405400000001</v>
       </c>
       <c r="O41">
-        <v>1.68681756625</v>
+        <v>1.67635135</v>
       </c>
       <c r="P41">
-        <v>5.060452698750001</v>
+        <v>5.029054050000001</v>
       </c>
       <c r="Q41">
-        <v>5.66045269875</v>
+        <v>5.629054050000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2529682695416079</v>
+        <v>0.2558376361557577</v>
       </c>
       <c r="T41">
-        <v>2.003475501528595</v>
+        <v>2.031224469693811</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.132508963585453</v>
+        <v>5.004196239495816</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1700925816934546</v>
+        <v>0.1696992689665283</v>
       </c>
       <c r="C42">
-        <v>54.73509039807504</v>
+        <v>54.24122527461213</v>
       </c>
       <c r="D42">
-        <v>82.90709039807504</v>
+        <v>83.17027527461214</v>
       </c>
       <c r="E42">
-        <v>30.177</v>
+        <v>30.93405</v>
       </c>
       <c r="F42">
-        <v>30.282</v>
+        <v>31.03905</v>
       </c>
       <c r="G42">
         <v>2.11</v>
@@ -4719,28 +4719,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M42">
-        <v>1.6745946</v>
+        <v>1.716459465</v>
       </c>
       <c r="N42">
-        <v>6.705405400000001</v>
+        <v>6.663540535000001</v>
       </c>
       <c r="O42">
-        <v>1.67635135</v>
+        <v>1.66588513375</v>
       </c>
       <c r="P42">
-        <v>5.029054050000001</v>
+        <v>4.99765540125</v>
       </c>
       <c r="Q42">
-        <v>5.629054050000001</v>
+        <v>5.59765540125</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2558376361557577</v>
+        <v>0.2588042694347938</v>
       </c>
       <c r="T42">
-        <v>2.031224469693811</v>
+        <v>2.059914080847679</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.004196239495816</v>
+        <v>4.882142672678844</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1696992689665283</v>
+        <v>0.1693059562396021</v>
       </c>
       <c r="C43">
-        <v>54.24122527461213</v>
+        <v>53.74903640976259</v>
       </c>
       <c r="D43">
-        <v>83.17027527461214</v>
+        <v>83.43513640976259</v>
       </c>
       <c r="E43">
-        <v>30.93405</v>
+        <v>31.6911</v>
       </c>
       <c r="F43">
-        <v>31.03905</v>
+        <v>31.7961</v>
       </c>
       <c r="G43">
         <v>2.11</v>
@@ -4801,28 +4801,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M43">
-        <v>1.716459465</v>
+        <v>1.75832433</v>
       </c>
       <c r="N43">
-        <v>6.663540535000001</v>
+        <v>6.62167567</v>
       </c>
       <c r="O43">
-        <v>1.66588513375</v>
+        <v>1.6554189175</v>
       </c>
       <c r="P43">
-        <v>4.99765540125</v>
+        <v>4.9662567525</v>
       </c>
       <c r="Q43">
-        <v>5.59765540125</v>
+        <v>5.566256752499999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2588042694347938</v>
+        <v>0.261873200413107</v>
       </c>
       <c r="T43">
-        <v>2.059914080847679</v>
+        <v>2.089592988937886</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.882142672678844</v>
+        <v>4.765901180472206</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1693059562396021</v>
+        <v>0.1689126435126758</v>
       </c>
       <c r="C44">
-        <v>53.74903640976258</v>
+        <v>53.25853986915125</v>
       </c>
       <c r="D44">
-        <v>83.43513640976258</v>
+        <v>83.70168986915125</v>
       </c>
       <c r="E44">
-        <v>31.6911</v>
+        <v>32.44815000000001</v>
       </c>
       <c r="F44">
-        <v>31.7961</v>
+        <v>32.55315</v>
       </c>
       <c r="G44">
         <v>2.11</v>
@@ -4883,28 +4883,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M44">
-        <v>1.75832433</v>
+        <v>1.800189195</v>
       </c>
       <c r="N44">
-        <v>6.621675670000001</v>
+        <v>6.579810805000001</v>
       </c>
       <c r="O44">
-        <v>1.6554189175</v>
+        <v>1.64495270125</v>
       </c>
       <c r="P44">
-        <v>4.966256752500001</v>
+        <v>4.934858103750001</v>
       </c>
       <c r="Q44">
-        <v>5.5662567525</v>
+        <v>5.53485810375</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.261873200413107</v>
+        <v>0.265049813180133</v>
       </c>
       <c r="T44">
-        <v>2.089592988937886</v>
+        <v>2.120313262224241</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.765901180472206</v>
+        <v>4.655066269298434</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1689126435126758</v>
+        <v>0.1685193307857495</v>
       </c>
       <c r="C45">
-        <v>53.25853986915125</v>
+        <v>52.76975192436283</v>
       </c>
       <c r="D45">
-        <v>83.70168986915125</v>
+        <v>83.96995192436283</v>
       </c>
       <c r="E45">
-        <v>32.44815000000001</v>
+        <v>33.2052</v>
       </c>
       <c r="F45">
-        <v>32.55315</v>
+        <v>33.3102</v>
       </c>
       <c r="G45">
         <v>2.11</v>
@@ -4965,28 +4965,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M45">
-        <v>1.800189195</v>
+        <v>1.84205406</v>
       </c>
       <c r="N45">
-        <v>6.579810805000001</v>
+        <v>6.53794594</v>
       </c>
       <c r="O45">
-        <v>1.64495270125</v>
+        <v>1.634486485</v>
       </c>
       <c r="P45">
-        <v>4.934858103750001</v>
+        <v>4.903459455</v>
       </c>
       <c r="Q45">
-        <v>5.53485810375</v>
+        <v>5.503459455</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.265049813180133</v>
+        <v>0.2683398764031242</v>
       </c>
       <c r="T45">
-        <v>2.120313262224241</v>
+        <v>2.152130688127967</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.655066269298434</v>
+        <v>4.54926930863256</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1685193307857495</v>
+        <v>0.1689697680588233</v>
       </c>
       <c r="C46">
-        <v>52.76975192436283</v>
+        <v>51.70562010744426</v>
       </c>
       <c r="D46">
-        <v>83.96995192436283</v>
+        <v>83.66287010744426</v>
       </c>
       <c r="E46">
-        <v>33.2052</v>
+        <v>33.96225</v>
       </c>
       <c r="F46">
-        <v>33.3102</v>
+        <v>34.06725</v>
       </c>
       <c r="G46">
         <v>2.11</v>
@@ -5047,45 +5047,45 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M46">
-        <v>1.84205406</v>
+        <v>1.96908705</v>
       </c>
       <c r="N46">
-        <v>6.53794594</v>
+        <v>6.41091295</v>
       </c>
       <c r="O46">
-        <v>1.634486485</v>
+        <v>1.6027282375</v>
       </c>
       <c r="P46">
-        <v>4.903459455</v>
+        <v>4.8081847125</v>
       </c>
       <c r="Q46">
-        <v>5.503459455</v>
+        <v>5.4081847125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2683398764031242</v>
+        <v>0.2717495782887696</v>
       </c>
       <c r="T46">
-        <v>2.152130688127967</v>
+        <v>2.185105111337282</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.54926930863256</v>
+        <v>4.255779347083715</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1689697680588233</v>
+        <v>0.168595205331897</v>
       </c>
       <c r="C47">
-        <v>51.70562010744426</v>
+        <v>51.20376730903873</v>
       </c>
       <c r="D47">
-        <v>83.66287010744426</v>
+        <v>83.91806730903873</v>
       </c>
       <c r="E47">
-        <v>33.96225</v>
+        <v>34.7193</v>
       </c>
       <c r="F47">
-        <v>34.06725</v>
+        <v>34.8243</v>
       </c>
       <c r="G47">
         <v>2.11</v>
@@ -5129,28 +5129,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M47">
-        <v>1.96908705</v>
+        <v>2.01284454</v>
       </c>
       <c r="N47">
-        <v>6.41091295</v>
+        <v>6.367155460000001</v>
       </c>
       <c r="O47">
-        <v>1.6027282375</v>
+        <v>1.591788865</v>
       </c>
       <c r="P47">
-        <v>4.8081847125</v>
+        <v>4.775366595000001</v>
       </c>
       <c r="Q47">
-        <v>5.4081847125</v>
+        <v>5.375366595000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2717495782887696</v>
+        <v>0.2752855654294389</v>
       </c>
       <c r="T47">
-        <v>2.185105111337282</v>
+        <v>2.219300809480275</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.255779347083715</v>
+        <v>4.163262404755809</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.168595205331897</v>
+        <v>0.1682206426049707</v>
       </c>
       <c r="C48">
-        <v>51.20376730903873</v>
+        <v>50.70347613223072</v>
       </c>
       <c r="D48">
-        <v>83.91806730903873</v>
+        <v>84.17482613223072</v>
       </c>
       <c r="E48">
-        <v>34.7193</v>
+        <v>35.47635</v>
       </c>
       <c r="F48">
-        <v>34.8243</v>
+        <v>35.58135</v>
       </c>
       <c r="G48">
         <v>2.11</v>
@@ -5211,28 +5211,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M48">
-        <v>2.01284454</v>
+        <v>2.05660203</v>
       </c>
       <c r="N48">
-        <v>6.367155460000001</v>
+        <v>6.32339797</v>
       </c>
       <c r="O48">
-        <v>1.591788865</v>
+        <v>1.5808494925</v>
       </c>
       <c r="P48">
-        <v>4.775366595000001</v>
+        <v>4.7425484775</v>
       </c>
       <c r="Q48">
-        <v>5.375366595000001</v>
+        <v>5.342548477499999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2752855654294389</v>
+        <v>0.2789549860471146</v>
       </c>
       <c r="T48">
-        <v>2.219300809480275</v>
+        <v>2.254786911326778</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.163262404755809</v>
+        <v>4.074682353590791</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1682206426049707</v>
+        <v>0.1691060798780445</v>
       </c>
       <c r="C49">
-        <v>50.70347613223072</v>
+        <v>49.3419828753719</v>
       </c>
       <c r="D49">
-        <v>84.17482613223072</v>
+        <v>83.57038287537191</v>
       </c>
       <c r="E49">
-        <v>35.47635</v>
+        <v>36.2334</v>
       </c>
       <c r="F49">
-        <v>35.58135</v>
+        <v>36.3384</v>
       </c>
       <c r="G49">
         <v>2.11</v>
@@ -5293,45 +5293,45 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M49">
-        <v>2.05660203</v>
+        <v>2.22754392</v>
       </c>
       <c r="N49">
-        <v>6.32339797</v>
+        <v>6.15245608</v>
       </c>
       <c r="O49">
-        <v>1.5808494925</v>
+        <v>1.53811402</v>
       </c>
       <c r="P49">
-        <v>4.7425484775</v>
+        <v>4.61434206</v>
       </c>
       <c r="Q49">
-        <v>5.342548477499999</v>
+        <v>5.21434206</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2789549860471146</v>
+        <v>0.2827655382270086</v>
       </c>
       <c r="T49">
-        <v>2.254786911326778</v>
+        <v>2.2916378632443</v>
       </c>
       <c r="U49">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.074682353590791</v>
+        <v>3.761990919577469</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1691060798780445</v>
+        <v>0.1687577671511182</v>
       </c>
       <c r="C50">
-        <v>49.3419828753719</v>
+        <v>48.82166967227403</v>
       </c>
       <c r="D50">
-        <v>83.57038287537191</v>
+        <v>83.80711967227403</v>
       </c>
       <c r="E50">
-        <v>36.2334</v>
+        <v>36.99045</v>
       </c>
       <c r="F50">
-        <v>36.3384</v>
+        <v>37.09545</v>
       </c>
       <c r="G50">
         <v>2.11</v>
@@ -5375,28 +5375,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M50">
-        <v>2.22754392</v>
+        <v>2.273951085</v>
       </c>
       <c r="N50">
-        <v>6.15245608</v>
+        <v>6.106048915000001</v>
       </c>
       <c r="O50">
-        <v>1.53811402</v>
+        <v>1.52651222875</v>
       </c>
       <c r="P50">
-        <v>4.61434206</v>
+        <v>4.57953668625</v>
       </c>
       <c r="Q50">
-        <v>5.21434206</v>
+        <v>5.17953668625</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2827655382270086</v>
+        <v>0.286725523825722</v>
       </c>
       <c r="T50">
-        <v>2.2916378632443</v>
+        <v>2.329933950531136</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.761990919577469</v>
+        <v>3.685215594688133</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1687577671511182</v>
+        <v>0.1684094544241919</v>
       </c>
       <c r="C51">
-        <v>48.82166967227403</v>
+        <v>48.30270152759241</v>
       </c>
       <c r="D51">
-        <v>83.80711967227403</v>
+        <v>84.04520152759241</v>
       </c>
       <c r="E51">
-        <v>36.99045</v>
+        <v>37.7475</v>
       </c>
       <c r="F51">
-        <v>37.09545</v>
+        <v>37.8525</v>
       </c>
       <c r="G51">
         <v>2.11</v>
@@ -5457,28 +5457,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M51">
-        <v>2.273951085</v>
+        <v>2.32035825</v>
       </c>
       <c r="N51">
-        <v>6.106048915000001</v>
+        <v>6.059641750000001</v>
       </c>
       <c r="O51">
-        <v>1.52651222875</v>
+        <v>1.5149104375</v>
       </c>
       <c r="P51">
-        <v>4.57953668625</v>
+        <v>4.544731312500001</v>
       </c>
       <c r="Q51">
-        <v>5.17953668625</v>
+        <v>5.1447313125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.286725523825722</v>
+        <v>0.2908439088483839</v>
       </c>
       <c r="T51">
-        <v>2.329933950531136</v>
+        <v>2.369761881309446</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.685215594688133</v>
+        <v>3.611511282794371</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1684094544241919</v>
+        <v>0.1680611416972657</v>
       </c>
       <c r="C52">
-        <v>48.30270152759241</v>
+        <v>47.78508993723548</v>
       </c>
       <c r="D52">
-        <v>84.04520152759241</v>
+        <v>84.28463993723548</v>
       </c>
       <c r="E52">
-        <v>37.7475</v>
+        <v>38.50455</v>
       </c>
       <c r="F52">
-        <v>37.8525</v>
+        <v>38.60955</v>
       </c>
       <c r="G52">
         <v>2.11</v>
@@ -5539,28 +5539,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M52">
-        <v>2.32035825</v>
+        <v>2.366765415</v>
       </c>
       <c r="N52">
-        <v>6.059641750000001</v>
+        <v>6.013234585000001</v>
       </c>
       <c r="O52">
-        <v>1.5149104375</v>
+        <v>1.50330864625</v>
       </c>
       <c r="P52">
-        <v>4.544731312500001</v>
+        <v>4.509925938750001</v>
       </c>
       <c r="Q52">
-        <v>5.1447313125</v>
+        <v>5.109925938750001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2908439088483839</v>
+        <v>0.2951303912189096</v>
       </c>
       <c r="T52">
-        <v>2.369761881309446</v>
+        <v>2.411215441915443</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.611511282794371</v>
+        <v>3.540697336072912</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1680611416972657</v>
+        <v>0.1688048289703394</v>
       </c>
       <c r="C53">
-        <v>47.78508993723548</v>
+        <v>46.51845495133191</v>
       </c>
       <c r="D53">
-        <v>84.28463993723548</v>
+        <v>83.77505495133191</v>
       </c>
       <c r="E53">
-        <v>38.50455</v>
+        <v>39.2616</v>
       </c>
       <c r="F53">
-        <v>38.60955</v>
+        <v>39.3666</v>
       </c>
       <c r="G53">
         <v>2.11</v>
@@ -5621,45 +5621,45 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M53">
-        <v>2.366765415</v>
+        <v>2.52339906</v>
       </c>
       <c r="N53">
-        <v>6.013234585000001</v>
+        <v>5.856600940000001</v>
       </c>
       <c r="O53">
-        <v>1.50330864625</v>
+        <v>1.464150235</v>
       </c>
       <c r="P53">
-        <v>4.509925938750001</v>
+        <v>4.392450705000001</v>
       </c>
       <c r="Q53">
-        <v>5.109925938750001</v>
+        <v>4.992450705</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2951303912189096</v>
+        <v>0.2995954770215405</v>
       </c>
       <c r="T53">
-        <v>2.411215441915443</v>
+        <v>2.454396234213355</v>
       </c>
       <c r="U53">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.540697336072912</v>
+        <v>3.320917461227873</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1688048289703394</v>
+        <v>0.1684775162434132</v>
       </c>
       <c r="C54">
-        <v>46.51845495133191</v>
+        <v>45.9849230215063</v>
       </c>
       <c r="D54">
-        <v>83.77505495133191</v>
+        <v>83.9985730215063</v>
       </c>
       <c r="E54">
-        <v>39.2616</v>
+        <v>40.01865</v>
       </c>
       <c r="F54">
-        <v>39.3666</v>
+        <v>40.12365</v>
       </c>
       <c r="G54">
         <v>2.11</v>
@@ -5703,28 +5703,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M54">
-        <v>2.52339906</v>
+        <v>2.571925965</v>
       </c>
       <c r="N54">
-        <v>5.856600940000001</v>
+        <v>5.808074035000001</v>
       </c>
       <c r="O54">
-        <v>1.464150235</v>
+        <v>1.45201850875</v>
       </c>
       <c r="P54">
-        <v>4.392450705000001</v>
+        <v>4.35605552625</v>
       </c>
       <c r="Q54">
-        <v>4.992450705</v>
+        <v>4.95605552625</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2995954770215405</v>
+        <v>0.3042505664753473</v>
       </c>
       <c r="T54">
-        <v>2.454396234213355</v>
+        <v>2.499414507034584</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.320917461227873</v>
+        <v>3.258258641204705</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1684775162434132</v>
+        <v>0.1681502035164869</v>
       </c>
       <c r="C55">
-        <v>45.9849230215063</v>
+        <v>45.4525870081069</v>
       </c>
       <c r="D55">
-        <v>83.9985730215063</v>
+        <v>84.22328700810691</v>
       </c>
       <c r="E55">
-        <v>40.01865</v>
+        <v>40.77570000000001</v>
       </c>
       <c r="F55">
-        <v>40.12365</v>
+        <v>40.8807</v>
       </c>
       <c r="G55">
         <v>2.11</v>
@@ -5785,28 +5785,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M55">
-        <v>2.571925965</v>
+        <v>2.62045287</v>
       </c>
       <c r="N55">
-        <v>5.808074035000001</v>
+        <v>5.759547130000001</v>
       </c>
       <c r="O55">
-        <v>1.45201850875</v>
+        <v>1.4398867825</v>
       </c>
       <c r="P55">
-        <v>4.35605552625</v>
+        <v>4.3196603475</v>
       </c>
       <c r="Q55">
-        <v>4.95605552625</v>
+        <v>4.9196603475</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3042505664753473</v>
+        <v>0.3091080511227977</v>
       </c>
       <c r="T55">
-        <v>2.499414507034584</v>
+        <v>2.54639009606543</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.258258641204705</v>
+        <v>3.197920518219433</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1681502035164869</v>
+        <v>0.1678228907895606</v>
       </c>
       <c r="C56">
-        <v>45.4525870081069</v>
+        <v>44.92145653486897</v>
       </c>
       <c r="D56">
-        <v>84.22328700810691</v>
+        <v>84.44920653486898</v>
       </c>
       <c r="E56">
-        <v>40.77570000000001</v>
+        <v>41.53275000000001</v>
       </c>
       <c r="F56">
-        <v>40.8807</v>
+        <v>41.63775</v>
       </c>
       <c r="G56">
         <v>2.11</v>
@@ -5867,28 +5867,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M56">
-        <v>2.62045287</v>
+        <v>2.668979775</v>
       </c>
       <c r="N56">
-        <v>5.759547130000001</v>
+        <v>5.711020225</v>
       </c>
       <c r="O56">
-        <v>1.4398867825</v>
+        <v>1.42775505625</v>
       </c>
       <c r="P56">
-        <v>4.3196603475</v>
+        <v>4.283265168750001</v>
       </c>
       <c r="Q56">
-        <v>4.9196603475</v>
+        <v>4.88326516875</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3091080511227977</v>
+        <v>0.3141814239768015</v>
       </c>
       <c r="T56">
-        <v>2.54639009606543</v>
+        <v>2.595453489053204</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.197920518219433</v>
+        <v>3.139776508797261</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1678228907895606</v>
+        <v>0.1674955780626344</v>
       </c>
       <c r="C57">
-        <v>44.92145653486897</v>
+        <v>44.3915413290639</v>
       </c>
       <c r="D57">
-        <v>84.44920653486898</v>
+        <v>84.6763413290639</v>
       </c>
       <c r="E57">
-        <v>41.53275000000001</v>
+        <v>42.28980000000001</v>
       </c>
       <c r="F57">
-        <v>41.63775</v>
+        <v>42.3948</v>
       </c>
       <c r="G57">
         <v>2.11</v>
@@ -5949,28 +5949,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M57">
-        <v>2.668979775</v>
+        <v>2.717506680000001</v>
       </c>
       <c r="N57">
-        <v>5.711020225</v>
+        <v>5.66249332</v>
       </c>
       <c r="O57">
-        <v>1.42775505625</v>
+        <v>1.41562333</v>
       </c>
       <c r="P57">
-        <v>4.283265168750001</v>
+        <v>4.24686999</v>
       </c>
       <c r="Q57">
-        <v>4.88326516875</v>
+        <v>4.84686999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3141814239768015</v>
+        <v>0.3194854046878055</v>
       </c>
       <c r="T57">
-        <v>2.595453489053204</v>
+        <v>2.646747036267694</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.139776508797261</v>
+        <v>3.083709071140167</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1674955780626344</v>
+        <v>0.1671682653357081</v>
       </c>
       <c r="C58">
-        <v>44.3915413290639</v>
+        <v>43.86285122289522</v>
       </c>
       <c r="D58">
-        <v>84.6763413290639</v>
+        <v>84.90470122289523</v>
       </c>
       <c r="E58">
-        <v>42.28980000000001</v>
+        <v>43.04685000000001</v>
       </c>
       <c r="F58">
-        <v>42.3948</v>
+        <v>43.15185</v>
       </c>
       <c r="G58">
         <v>2.11</v>
@@ -6031,28 +6031,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M58">
-        <v>2.717506680000001</v>
+        <v>2.766033585</v>
       </c>
       <c r="N58">
-        <v>5.66249332</v>
+        <v>5.613966415</v>
       </c>
       <c r="O58">
-        <v>1.41562333</v>
+        <v>1.40349160375</v>
       </c>
       <c r="P58">
-        <v>4.24686999</v>
+        <v>4.21047481125</v>
       </c>
       <c r="Q58">
-        <v>4.84686999</v>
+        <v>4.81047481125</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3194854046878055</v>
+        <v>0.3250360821760654</v>
       </c>
       <c r="T58">
-        <v>2.646747036267694</v>
+        <v>2.700426329864253</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.083709071140167</v>
+        <v>3.029608911997357</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1671682653357081</v>
+        <v>0.1702339526087819</v>
       </c>
       <c r="C59">
-        <v>43.86285122289522</v>
+        <v>41.01399865208472</v>
       </c>
       <c r="D59">
-        <v>84.90470122289523</v>
+        <v>82.81289865208473</v>
       </c>
       <c r="E59">
-        <v>43.04685000000001</v>
+        <v>43.80390000000001</v>
       </c>
       <c r="F59">
-        <v>43.15185</v>
+        <v>43.9089</v>
       </c>
       <c r="G59">
         <v>2.11</v>
@@ -6113,45 +6113,45 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M59">
-        <v>2.766033585</v>
+        <v>3.15704991</v>
       </c>
       <c r="N59">
-        <v>5.613966415</v>
+        <v>5.22295009</v>
       </c>
       <c r="O59">
-        <v>1.40349160375</v>
+        <v>1.3057375225</v>
       </c>
       <c r="P59">
-        <v>4.21047481125</v>
+        <v>3.9172125675</v>
       </c>
       <c r="Q59">
-        <v>4.81047481125</v>
+        <v>4.5172125675</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3250360821760654</v>
+        <v>0.3308510776399569</v>
       </c>
       <c r="T59">
-        <v>2.700426329864253</v>
+        <v>2.756661780298745</v>
       </c>
       <c r="U59">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.029608911997357</v>
+        <v>2.654376788107224</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1702339526087819</v>
+        <v>0.1699651398818556</v>
       </c>
       <c r="C60">
-        <v>41.01399865208473</v>
+        <v>40.43623537565722</v>
       </c>
       <c r="D60">
-        <v>82.81289865208473</v>
+        <v>82.99218537565721</v>
       </c>
       <c r="E60">
-        <v>43.8039</v>
+        <v>44.56095</v>
       </c>
       <c r="F60">
-        <v>43.9089</v>
+        <v>44.66595</v>
       </c>
       <c r="G60">
         <v>2.11</v>
@@ -6195,28 +6195,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M60">
-        <v>3.15704991</v>
+        <v>3.211481805</v>
       </c>
       <c r="N60">
-        <v>5.222950090000001</v>
+        <v>5.168518195000001</v>
       </c>
       <c r="O60">
-        <v>1.3057375225</v>
+        <v>1.29212954875</v>
       </c>
       <c r="P60">
-        <v>3.917212567500001</v>
+        <v>3.876388646250001</v>
       </c>
       <c r="Q60">
-        <v>4.517212567500001</v>
+        <v>4.47638864625</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3308510776399568</v>
+        <v>0.33694973141916</v>
       </c>
       <c r="T60">
-        <v>2.756661780298744</v>
+        <v>2.815640423437356</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.654376788107224</v>
+        <v>2.609387351020661</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1699651398818556</v>
+        <v>0.1696963271549294</v>
       </c>
       <c r="C61">
-        <v>40.43623537565722</v>
+        <v>39.85925008117913</v>
       </c>
       <c r="D61">
-        <v>82.99218537565721</v>
+        <v>83.17225008117913</v>
       </c>
       <c r="E61">
-        <v>44.56095</v>
+        <v>45.318</v>
       </c>
       <c r="F61">
-        <v>44.66595</v>
+        <v>45.42299999999999</v>
       </c>
       <c r="G61">
         <v>2.11</v>
@@ -6277,28 +6277,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M61">
-        <v>3.211481805</v>
+        <v>3.2659137</v>
       </c>
       <c r="N61">
-        <v>5.168518195000001</v>
+        <v>5.1140863</v>
       </c>
       <c r="O61">
-        <v>1.29212954875</v>
+        <v>1.278521575</v>
       </c>
       <c r="P61">
-        <v>3.876388646250001</v>
+        <v>3.835564725</v>
       </c>
       <c r="Q61">
-        <v>4.47638864625</v>
+        <v>4.435564725</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.33694973141916</v>
+        <v>0.3433533178873234</v>
       </c>
       <c r="T61">
-        <v>2.815640423437356</v>
+        <v>2.877567998732899</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.609387351020661</v>
+        <v>2.565897561836983</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1696963271549294</v>
+        <v>0.1694275144280031</v>
       </c>
       <c r="C62">
-        <v>39.85925008117913</v>
+        <v>39.28304784352682</v>
       </c>
       <c r="D62">
-        <v>83.17225008117913</v>
+        <v>83.35309784352683</v>
       </c>
       <c r="E62">
-        <v>45.318</v>
+        <v>46.07505</v>
       </c>
       <c r="F62">
-        <v>45.42299999999999</v>
+        <v>46.18005</v>
       </c>
       <c r="G62">
         <v>2.11</v>
@@ -6359,28 +6359,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M62">
-        <v>3.2659137</v>
+        <v>3.320345595</v>
       </c>
       <c r="N62">
-        <v>5.1140863</v>
+        <v>5.059654405</v>
       </c>
       <c r="O62">
-        <v>1.278521575</v>
+        <v>1.26491360125</v>
       </c>
       <c r="P62">
-        <v>3.835564725</v>
+        <v>3.79474080375</v>
       </c>
       <c r="Q62">
-        <v>4.435564725</v>
+        <v>4.39474080375</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3433533178873234</v>
+        <v>0.3500852934051362</v>
       </c>
       <c r="T62">
-        <v>2.877567998732899</v>
+        <v>2.942671347120522</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.565897561836983</v>
+        <v>2.523833667380639</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1694275144280031</v>
+        <v>0.1709722017010768</v>
       </c>
       <c r="C63">
-        <v>39.28304784352682</v>
+        <v>37.49737912738695</v>
       </c>
       <c r="D63">
-        <v>83.35309784352683</v>
+        <v>82.32447912738695</v>
       </c>
       <c r="E63">
-        <v>46.07505</v>
+        <v>46.8321</v>
       </c>
       <c r="F63">
-        <v>46.18005</v>
+        <v>46.9371</v>
       </c>
       <c r="G63">
         <v>2.11</v>
@@ -6441,45 +6441,45 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M63">
-        <v>3.320345595</v>
+        <v>3.557832180000001</v>
       </c>
       <c r="N63">
-        <v>5.059654405</v>
+        <v>4.822167820000001</v>
       </c>
       <c r="O63">
-        <v>1.26491360125</v>
+        <v>1.205541955</v>
       </c>
       <c r="P63">
-        <v>3.79474080375</v>
+        <v>3.616625865</v>
       </c>
       <c r="Q63">
-        <v>4.39474080375</v>
+        <v>4.216625865</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3500852934051362</v>
+        <v>0.3571715834238864</v>
       </c>
       <c r="T63">
-        <v>2.942671347120522</v>
+        <v>3.011201187528545</v>
       </c>
       <c r="U63">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.523833667380639</v>
+        <v>2.355366857129276</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1709722017010768</v>
+        <v>0.1707326389741506</v>
       </c>
       <c r="C64">
-        <v>37.49737912738695</v>
+        <v>36.89818921002414</v>
       </c>
       <c r="D64">
-        <v>82.32447912738695</v>
+        <v>82.48233921002414</v>
       </c>
       <c r="E64">
-        <v>46.8321</v>
+        <v>47.58915</v>
       </c>
       <c r="F64">
-        <v>46.9371</v>
+        <v>47.69415</v>
       </c>
       <c r="G64">
         <v>2.11</v>
@@ -6523,28 +6523,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M64">
-        <v>3.557832180000001</v>
+        <v>3.61521657</v>
       </c>
       <c r="N64">
-        <v>4.822167820000001</v>
+        <v>4.76478343</v>
       </c>
       <c r="O64">
-        <v>1.205541955</v>
+        <v>1.1911958575</v>
       </c>
       <c r="P64">
-        <v>3.616625865</v>
+        <v>3.5735875725</v>
       </c>
       <c r="Q64">
-        <v>4.216625865</v>
+        <v>4.1735875725</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3571715834238864</v>
+        <v>0.3646409161463529</v>
       </c>
       <c r="T64">
-        <v>3.011201187528545</v>
+        <v>3.083435343634299</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.355366857129276</v>
+        <v>2.317980081619287</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1707326389741506</v>
+        <v>0.1704930762472243</v>
       </c>
       <c r="C65">
-        <v>36.89818921002414</v>
+        <v>36.29960586029132</v>
       </c>
       <c r="D65">
-        <v>82.48233921002414</v>
+        <v>82.64080586029132</v>
       </c>
       <c r="E65">
-        <v>47.58915</v>
+        <v>48.3462</v>
       </c>
       <c r="F65">
-        <v>47.69415</v>
+        <v>48.4512</v>
       </c>
       <c r="G65">
         <v>2.11</v>
@@ -6605,28 +6605,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M65">
-        <v>3.61521657</v>
+        <v>3.67260096</v>
       </c>
       <c r="N65">
-        <v>4.76478343</v>
+        <v>4.70739904</v>
       </c>
       <c r="O65">
-        <v>1.1911958575</v>
+        <v>1.17684976</v>
       </c>
       <c r="P65">
-        <v>3.5735875725</v>
+        <v>3.53054928</v>
       </c>
       <c r="Q65">
-        <v>4.1735875725</v>
+        <v>4.13054928</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3646409161463529</v>
+        <v>0.3725252117978453</v>
       </c>
       <c r="T65">
-        <v>3.083435343634299</v>
+        <v>3.159682508412596</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.317980081619287</v>
+        <v>2.281761642843986</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1704930762472243</v>
+        <v>0.170253513520298</v>
       </c>
       <c r="C66">
-        <v>36.29960586029132</v>
+        <v>35.70163258096623</v>
       </c>
       <c r="D66">
-        <v>82.64080586029132</v>
+        <v>82.79988258096623</v>
       </c>
       <c r="E66">
-        <v>48.3462</v>
+        <v>49.10325</v>
       </c>
       <c r="F66">
-        <v>48.4512</v>
+        <v>49.20825</v>
       </c>
       <c r="G66">
         <v>2.11</v>
@@ -6687,28 +6687,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M66">
-        <v>3.67260096</v>
+        <v>3.72998535</v>
       </c>
       <c r="N66">
-        <v>4.70739904</v>
+        <v>4.650014650000001</v>
       </c>
       <c r="O66">
-        <v>1.17684976</v>
+        <v>1.1625036625</v>
       </c>
       <c r="P66">
-        <v>3.53054928</v>
+        <v>3.487510987500001</v>
       </c>
       <c r="Q66">
-        <v>4.13054928</v>
+        <v>4.0875109875</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3725252117978453</v>
+        <v>0.380860038629423</v>
       </c>
       <c r="T66">
-        <v>3.159682508412596</v>
+        <v>3.240286654035366</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.281761642843986</v>
+        <v>2.246657617569463</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.170253513520298</v>
+        <v>0.1700139507933718</v>
       </c>
       <c r="C67">
-        <v>35.70163258096623</v>
+        <v>35.10427290184867</v>
       </c>
       <c r="D67">
-        <v>82.79988258096623</v>
+        <v>82.95957290184867</v>
       </c>
       <c r="E67">
-        <v>49.10325</v>
+        <v>49.8603</v>
       </c>
       <c r="F67">
-        <v>49.20825</v>
+        <v>49.9653</v>
       </c>
       <c r="G67">
         <v>2.11</v>
@@ -6769,28 +6769,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M67">
-        <v>3.72998535</v>
+        <v>3.78736974</v>
       </c>
       <c r="N67">
-        <v>4.650014650000001</v>
+        <v>4.59263026</v>
       </c>
       <c r="O67">
-        <v>1.1625036625</v>
+        <v>1.148157565</v>
       </c>
       <c r="P67">
-        <v>3.487510987500001</v>
+        <v>3.444472695</v>
       </c>
       <c r="Q67">
-        <v>4.0875109875</v>
+        <v>4.044472695</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.380860038629423</v>
+        <v>0.3896851493922699</v>
       </c>
       <c r="T67">
-        <v>3.240286654035366</v>
+        <v>3.325632219988887</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.246657617569463</v>
+        <v>2.212617350636592</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1700139507933718</v>
+        <v>0.1697743880664455</v>
       </c>
       <c r="C68">
-        <v>35.10427290184867</v>
+        <v>34.50753038002194</v>
       </c>
       <c r="D68">
-        <v>82.95957290184867</v>
+        <v>83.11988038002194</v>
       </c>
       <c r="E68">
-        <v>49.8603</v>
+        <v>50.61735</v>
       </c>
       <c r="F68">
-        <v>49.9653</v>
+        <v>50.72235</v>
       </c>
       <c r="G68">
         <v>2.11</v>
@@ -6851,28 +6851,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M68">
-        <v>3.78736974</v>
+        <v>3.84475413</v>
       </c>
       <c r="N68">
-        <v>4.59263026</v>
+        <v>4.535245870000001</v>
       </c>
       <c r="O68">
-        <v>1.148157565</v>
+        <v>1.1338114675</v>
       </c>
       <c r="P68">
-        <v>3.444472695</v>
+        <v>3.401434402500001</v>
       </c>
       <c r="Q68">
-        <v>4.044472695</v>
+        <v>4.0014344025</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3896851493922699</v>
+        <v>0.3990451153528652</v>
       </c>
       <c r="T68">
-        <v>3.325632219988887</v>
+        <v>3.416150244485046</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.212617350636592</v>
+        <v>2.179593211074852</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1697743880664455</v>
+        <v>0.1695348253395192</v>
       </c>
       <c r="C69">
-        <v>34.50753038002194</v>
+        <v>33.91140860011669</v>
       </c>
       <c r="D69">
-        <v>83.11988038002194</v>
+        <v>83.2808086001167</v>
       </c>
       <c r="E69">
-        <v>50.61735</v>
+        <v>51.37440000000001</v>
       </c>
       <c r="F69">
-        <v>50.72235</v>
+        <v>51.47940000000001</v>
       </c>
       <c r="G69">
         <v>2.11</v>
@@ -6933,28 +6933,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M69">
-        <v>3.84475413</v>
+        <v>3.902138520000001</v>
       </c>
       <c r="N69">
-        <v>4.535245870000001</v>
+        <v>4.47786148</v>
       </c>
       <c r="O69">
-        <v>1.1338114675</v>
+        <v>1.11946537</v>
       </c>
       <c r="P69">
-        <v>3.401434402500001</v>
+        <v>3.35839611</v>
       </c>
       <c r="Q69">
-        <v>4.0014344025</v>
+        <v>3.958396109999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3990451153528652</v>
+        <v>0.4089900791859977</v>
       </c>
       <c r="T69">
-        <v>3.416150244485046</v>
+        <v>3.512325645512216</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.179593211074852</v>
+        <v>2.147540369735516</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1695348253395192</v>
+        <v>0.169295262612593</v>
       </c>
       <c r="C70">
-        <v>33.91140860011669</v>
+        <v>33.3159111745782</v>
       </c>
       <c r="D70">
-        <v>83.2808086001167</v>
+        <v>83.44236117457821</v>
       </c>
       <c r="E70">
-        <v>51.37440000000001</v>
+        <v>52.13145000000001</v>
       </c>
       <c r="F70">
-        <v>51.47940000000001</v>
+        <v>52.23645</v>
       </c>
       <c r="G70">
         <v>2.11</v>
@@ -7015,28 +7015,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M70">
-        <v>3.902138520000001</v>
+        <v>3.959522910000001</v>
       </c>
       <c r="N70">
-        <v>4.47786148</v>
+        <v>4.42047709</v>
       </c>
       <c r="O70">
-        <v>1.11946537</v>
+        <v>1.1051192725</v>
       </c>
       <c r="P70">
-        <v>3.35839611</v>
+        <v>3.3153578175</v>
       </c>
       <c r="Q70">
-        <v>3.958396109999999</v>
+        <v>3.9153578175</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4089900791859977</v>
+        <v>0.4195766535890097</v>
       </c>
       <c r="T70">
-        <v>3.512325645512216</v>
+        <v>3.614705911121783</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.147540369735516</v>
+        <v>2.116416596261089</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.169295262612593</v>
+        <v>0.1690556998856667</v>
       </c>
       <c r="C71">
-        <v>33.3159111745782</v>
+        <v>32.72104174393679</v>
       </c>
       <c r="D71">
-        <v>83.44236117457821</v>
+        <v>83.60454174393679</v>
       </c>
       <c r="E71">
-        <v>52.13145000000001</v>
+        <v>52.88850000000001</v>
       </c>
       <c r="F71">
-        <v>52.23645</v>
+        <v>52.9935</v>
       </c>
       <c r="G71">
         <v>2.11</v>
@@ -7097,28 +7097,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M71">
-        <v>3.959522910000001</v>
+        <v>4.016907300000001</v>
       </c>
       <c r="N71">
-        <v>4.42047709</v>
+        <v>4.3630927</v>
       </c>
       <c r="O71">
-        <v>1.1051192725</v>
+        <v>1.090773175</v>
       </c>
       <c r="P71">
-        <v>3.3153578175</v>
+        <v>3.272319525</v>
       </c>
       <c r="Q71">
-        <v>3.9153578175</v>
+        <v>3.872319525</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4195766535890097</v>
+        <v>0.4308689996188891</v>
       </c>
       <c r="T71">
-        <v>3.614705911121783</v>
+        <v>3.723911527771988</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.116416596261089</v>
+        <v>2.086182073457358</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1690556998856667</v>
+        <v>0.1688161371587404</v>
       </c>
       <c r="C72">
-        <v>32.72104174393679</v>
+        <v>32.12680397708108</v>
       </c>
       <c r="D72">
-        <v>83.60454174393679</v>
+        <v>83.76735397708109</v>
       </c>
       <c r="E72">
-        <v>52.88850000000001</v>
+        <v>53.64555000000001</v>
       </c>
       <c r="F72">
-        <v>52.9935</v>
+        <v>53.75055</v>
       </c>
       <c r="G72">
         <v>2.11</v>
@@ -7179,28 +7179,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M72">
-        <v>4.016907300000001</v>
+        <v>4.074291690000001</v>
       </c>
       <c r="N72">
-        <v>4.3630927</v>
+        <v>4.30570831</v>
       </c>
       <c r="O72">
-        <v>1.090773175</v>
+        <v>1.0764270775</v>
       </c>
       <c r="P72">
-        <v>3.272319525</v>
+        <v>3.2292812325</v>
       </c>
       <c r="Q72">
-        <v>3.872319525</v>
+        <v>3.8292812325</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4308689996188891</v>
+        <v>0.4429401281335879</v>
       </c>
       <c r="T72">
-        <v>3.723911527771988</v>
+        <v>3.840648566260139</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.086182073457358</v>
+        <v>2.056799227352325</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1688161371587405</v>
+        <v>0.1685765744318142</v>
       </c>
       <c r="C73">
-        <v>32.12680397708107</v>
+        <v>31.5332015715348</v>
       </c>
       <c r="D73">
-        <v>83.76735397708107</v>
+        <v>83.9308015715348</v>
       </c>
       <c r="E73">
-        <v>53.64555</v>
+        <v>54.4026</v>
       </c>
       <c r="F73">
-        <v>53.75055</v>
+        <v>54.5076</v>
       </c>
       <c r="G73">
         <v>2.11</v>
@@ -7261,28 +7261,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M73">
-        <v>4.07429169</v>
+        <v>4.13167608</v>
       </c>
       <c r="N73">
-        <v>4.305708310000001</v>
+        <v>4.248323920000001</v>
       </c>
       <c r="O73">
-        <v>1.0764270775</v>
+        <v>1.06208098</v>
       </c>
       <c r="P73">
-        <v>3.229281232500001</v>
+        <v>3.186242940000001</v>
       </c>
       <c r="Q73">
-        <v>3.829281232500001</v>
+        <v>3.78624294</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4429401281335878</v>
+        <v>0.4558734801136221</v>
       </c>
       <c r="T73">
-        <v>3.840648566260138</v>
+        <v>3.965723964640298</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.056799227352326</v>
+        <v>2.028232571416877</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1685765744318142</v>
+        <v>0.1683370117048879</v>
       </c>
       <c r="C74">
-        <v>31.5332015715348</v>
+        <v>30.94023825373664</v>
       </c>
       <c r="D74">
-        <v>83.9308015715348</v>
+        <v>84.09488825373664</v>
       </c>
       <c r="E74">
-        <v>54.4026</v>
+        <v>55.15965</v>
       </c>
       <c r="F74">
-        <v>54.5076</v>
+        <v>55.26465</v>
       </c>
       <c r="G74">
         <v>2.11</v>
@@ -7343,28 +7343,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M74">
-        <v>4.13167608</v>
+        <v>4.18906047</v>
       </c>
       <c r="N74">
-        <v>4.248323920000001</v>
+        <v>4.190939530000001</v>
       </c>
       <c r="O74">
-        <v>1.06208098</v>
+        <v>1.0477348825</v>
       </c>
       <c r="P74">
-        <v>3.186242940000001</v>
+        <v>3.1432046475</v>
       </c>
       <c r="Q74">
-        <v>3.78624294</v>
+        <v>3.7432046475</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4558734801136221</v>
+        <v>0.4697648581662516</v>
       </c>
       <c r="T74">
-        <v>3.965723964640298</v>
+        <v>4.100064207344915</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.028232571416877</v>
+        <v>2.000448563589248</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1683370117048879</v>
+        <v>0.1759784489779616</v>
       </c>
       <c r="C75">
-        <v>30.94023825373664</v>
+        <v>25.24684265565796</v>
       </c>
       <c r="D75">
-        <v>84.09488825373664</v>
+        <v>79.15854265565795</v>
       </c>
       <c r="E75">
-        <v>55.15965</v>
+        <v>55.9167</v>
       </c>
       <c r="F75">
-        <v>55.26465</v>
+        <v>56.0217</v>
       </c>
       <c r="G75">
         <v>2.11</v>
@@ -7425,45 +7425,45 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M75">
-        <v>4.18906047</v>
+        <v>5.041952999999999</v>
       </c>
       <c r="N75">
-        <v>4.190939530000001</v>
+        <v>3.338047000000001</v>
       </c>
       <c r="O75">
-        <v>1.0477348825</v>
+        <v>0.8345117500000003</v>
       </c>
       <c r="P75">
-        <v>3.1432046475</v>
+        <v>2.503535250000001</v>
       </c>
       <c r="Q75">
-        <v>3.7432046475</v>
+        <v>3.103535250000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4697648581662516</v>
+        <v>0.4847248037613909</v>
       </c>
       <c r="T75">
-        <v>4.100064207344915</v>
+        <v>4.244738314872964</v>
       </c>
       <c r="U75">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.000448563589248</v>
+        <v>1.662054366631343</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1759784489779616</v>
+        <v>0.1758453862510354</v>
       </c>
       <c r="C76">
-        <v>25.24684265565796</v>
+        <v>24.57078785163466</v>
       </c>
       <c r="D76">
-        <v>79.15854265565795</v>
+        <v>79.23953785163467</v>
       </c>
       <c r="E76">
-        <v>55.9167</v>
+        <v>56.67375000000001</v>
       </c>
       <c r="F76">
-        <v>56.0217</v>
+        <v>56.77875</v>
       </c>
       <c r="G76">
         <v>2.11</v>
@@ -7507,28 +7507,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M76">
-        <v>5.041952999999999</v>
+        <v>5.1100875</v>
       </c>
       <c r="N76">
-        <v>3.338047000000001</v>
+        <v>3.269912500000001</v>
       </c>
       <c r="O76">
-        <v>0.8345117500000003</v>
+        <v>0.8174781250000003</v>
       </c>
       <c r="P76">
-        <v>2.503535250000001</v>
+        <v>2.452434375000001</v>
       </c>
       <c r="Q76">
-        <v>3.103535250000001</v>
+        <v>3.052434375000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4847248037613909</v>
+        <v>0.5008815450041416</v>
       </c>
       <c r="T76">
-        <v>4.244738314872964</v>
+        <v>4.400986351003258</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.662054366631343</v>
+        <v>1.639893641742925</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1758453862510354</v>
+        <v>0.1757123235241091</v>
       </c>
       <c r="C77">
-        <v>24.57078785163466</v>
+        <v>23.89489896630719</v>
       </c>
       <c r="D77">
-        <v>79.23953785163467</v>
+        <v>79.32069896630719</v>
       </c>
       <c r="E77">
-        <v>56.67375000000001</v>
+        <v>57.4308</v>
       </c>
       <c r="F77">
-        <v>56.77875</v>
+        <v>57.5358</v>
       </c>
       <c r="G77">
         <v>2.11</v>
@@ -7589,28 +7589,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M77">
-        <v>5.1100875</v>
+        <v>5.178222</v>
       </c>
       <c r="N77">
-        <v>3.269912500000001</v>
+        <v>3.201778000000001</v>
       </c>
       <c r="O77">
-        <v>0.8174781250000003</v>
+        <v>0.8004445000000002</v>
       </c>
       <c r="P77">
-        <v>2.452434375000001</v>
+        <v>2.401333500000001</v>
       </c>
       <c r="Q77">
-        <v>3.052434375000001</v>
+        <v>3.0013335</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5008815450041416</v>
+        <v>0.5183846813504547</v>
       </c>
       <c r="T77">
-        <v>4.400986351003258</v>
+        <v>4.570255056811075</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.639893641742925</v>
+        <v>1.618316093825255</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1757123235241091</v>
+        <v>0.1755792607971829</v>
       </c>
       <c r="C78">
-        <v>23.89489896630719</v>
+        <v>23.21917651002504</v>
       </c>
       <c r="D78">
-        <v>79.32069896630719</v>
+        <v>79.40202651002504</v>
       </c>
       <c r="E78">
-        <v>57.4308</v>
+        <v>58.18785</v>
       </c>
       <c r="F78">
-        <v>57.5358</v>
+        <v>58.29285</v>
       </c>
       <c r="G78">
         <v>2.11</v>
@@ -7671,28 +7671,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M78">
-        <v>5.178222</v>
+        <v>5.2463565</v>
       </c>
       <c r="N78">
-        <v>3.201778000000001</v>
+        <v>3.133643500000001</v>
       </c>
       <c r="O78">
-        <v>0.8004445000000002</v>
+        <v>0.7834108750000002</v>
       </c>
       <c r="P78">
-        <v>2.401333500000001</v>
+        <v>2.350232625</v>
       </c>
       <c r="Q78">
-        <v>3.0013335</v>
+        <v>2.950232625</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5183846813504547</v>
+        <v>0.537409829552969</v>
       </c>
       <c r="T78">
-        <v>4.570255056811075</v>
+        <v>4.754242780515225</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.618316093825255</v>
+        <v>1.597299001697654</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1755792607971829</v>
+        <v>0.1754461980702566</v>
       </c>
       <c r="C79">
-        <v>23.21917651002504</v>
+        <v>22.54362099523293</v>
       </c>
       <c r="D79">
-        <v>79.40202651002504</v>
+        <v>79.48352099523294</v>
       </c>
       <c r="E79">
-        <v>58.18785</v>
+        <v>58.9449</v>
       </c>
       <c r="F79">
-        <v>58.29285</v>
+        <v>59.0499</v>
       </c>
       <c r="G79">
         <v>2.11</v>
@@ -7753,28 +7753,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M79">
-        <v>5.2463565</v>
+        <v>5.314491</v>
       </c>
       <c r="N79">
-        <v>3.133643500000001</v>
+        <v>3.065509</v>
       </c>
       <c r="O79">
-        <v>0.7834108750000002</v>
+        <v>0.7663772500000001</v>
       </c>
       <c r="P79">
-        <v>2.350232625</v>
+        <v>2.29913175</v>
       </c>
       <c r="Q79">
-        <v>2.950232625</v>
+        <v>2.89913175</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.537409829552969</v>
+        <v>0.5581645366829846</v>
       </c>
       <c r="T79">
-        <v>4.754242780515225</v>
+        <v>4.954956660919752</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.597299001697654</v>
+        <v>1.576820809368197</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1754461980702566</v>
+        <v>0.1753131353433303</v>
       </c>
       <c r="C80">
-        <v>22.54362099523293</v>
+        <v>21.8682329364815</v>
       </c>
       <c r="D80">
-        <v>79.48352099523294</v>
+        <v>79.56518293648151</v>
       </c>
       <c r="E80">
-        <v>58.9449</v>
+        <v>59.70195</v>
       </c>
       <c r="F80">
-        <v>59.0499</v>
+        <v>59.80695</v>
       </c>
       <c r="G80">
         <v>2.11</v>
@@ -7835,28 +7835,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M80">
-        <v>5.314491</v>
+        <v>5.3826255</v>
       </c>
       <c r="N80">
-        <v>3.065509</v>
+        <v>2.997374500000001</v>
       </c>
       <c r="O80">
-        <v>0.7663772500000001</v>
+        <v>0.7493436250000003</v>
       </c>
       <c r="P80">
-        <v>2.29913175</v>
+        <v>2.248030875000001</v>
       </c>
       <c r="Q80">
-        <v>2.89913175</v>
+        <v>2.848030875000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5581645366829846</v>
+        <v>0.5808958825872874</v>
       </c>
       <c r="T80">
-        <v>4.954956660919752</v>
+        <v>5.174786148981854</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.576820809368197</v>
+        <v>1.556861052287587</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1753131353433303</v>
+        <v>0.1751800726164041</v>
       </c>
       <c r="C81">
-        <v>21.8682329364815</v>
+        <v>21.19301285043826</v>
       </c>
       <c r="D81">
-        <v>79.56518293648151</v>
+        <v>79.64701285043826</v>
       </c>
       <c r="E81">
-        <v>59.70195</v>
+        <v>60.459</v>
       </c>
       <c r="F81">
-        <v>59.80695</v>
+        <v>60.564</v>
       </c>
       <c r="G81">
         <v>2.11</v>
@@ -7917,28 +7917,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M81">
-        <v>5.3826255</v>
+        <v>5.45076</v>
       </c>
       <c r="N81">
-        <v>2.997374500000001</v>
+        <v>2.929240000000001</v>
       </c>
       <c r="O81">
-        <v>0.7493436250000003</v>
+        <v>0.7323100000000002</v>
       </c>
       <c r="P81">
-        <v>2.248030875000001</v>
+        <v>2.196930000000001</v>
       </c>
       <c r="Q81">
-        <v>2.848030875000001</v>
+        <v>2.796930000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5808958825872874</v>
+        <v>0.6059003630820204</v>
       </c>
       <c r="T81">
-        <v>5.174786148981854</v>
+        <v>5.416598585850164</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.556861052287587</v>
+        <v>1.537400289133993</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1751800726164041</v>
+        <v>0.1750470098894778</v>
       </c>
       <c r="C82">
-        <v>21.19301285043826</v>
+        <v>20.51796125589824</v>
       </c>
       <c r="D82">
-        <v>79.64701285043826</v>
+        <v>79.72901125589824</v>
       </c>
       <c r="E82">
-        <v>60.459</v>
+        <v>61.21605</v>
       </c>
       <c r="F82">
-        <v>60.564</v>
+        <v>61.32105</v>
       </c>
       <c r="G82">
         <v>2.11</v>
@@ -7999,28 +7999,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M82">
-        <v>5.45076</v>
+        <v>5.5188945</v>
       </c>
       <c r="N82">
-        <v>2.929240000000001</v>
+        <v>2.861105500000001</v>
       </c>
       <c r="O82">
-        <v>0.7323100000000002</v>
+        <v>0.7152763750000002</v>
       </c>
       <c r="P82">
-        <v>2.196930000000001</v>
+        <v>2.145829125000001</v>
       </c>
       <c r="Q82">
-        <v>2.796930000000001</v>
+        <v>2.745829125</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6059003630820204</v>
+        <v>0.6335368941551466</v>
       </c>
       <c r="T82">
-        <v>5.416598585850164</v>
+        <v>5.683864963441456</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.537400289133993</v>
+        <v>1.518420038650857</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1750470098894778</v>
+        <v>0.2145758156024789</v>
       </c>
       <c r="C83">
-        <v>20.51796125589824</v>
+        <v>1.087663644124945</v>
       </c>
       <c r="D83">
-        <v>79.72901125589824</v>
+        <v>61.05576364412495</v>
       </c>
       <c r="E83">
-        <v>61.21605</v>
+        <v>61.97310000000001</v>
       </c>
       <c r="F83">
-        <v>61.32105</v>
+        <v>62.07810000000001</v>
       </c>
       <c r="G83">
         <v>2.11</v>
@@ -8081,45 +8081,45 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M83">
-        <v>5.5188945</v>
+        <v>9.113065080000002</v>
       </c>
       <c r="N83">
-        <v>2.861105500000001</v>
+        <v>-0.7330650800000011</v>
       </c>
       <c r="O83">
-        <v>0.7152763750000002</v>
+        <v>-0.1832662700000003</v>
       </c>
       <c r="P83">
-        <v>2.145829125000001</v>
+        <v>-0.5497988100000009</v>
       </c>
       <c r="Q83">
-        <v>2.745829125</v>
+        <v>0.05020118999999879</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6335368941551466</v>
+        <v>0.67707233781606</v>
       </c>
       <c r="T83">
-        <v>5.683864963441456</v>
+        <v>6.104885977015645</v>
       </c>
       <c r="U83">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.25</v>
+        <v>0.2298897222404122</v>
       </c>
       <c r="W83">
-        <v>0.0675</v>
+        <v>0.1130521887751075</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>1.518420038650857</v>
+        <v>0.9195588889616488</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2145758156024789</v>
+        <v>0.2155858156024789</v>
       </c>
       <c r="C84">
-        <v>1.087663644124945</v>
+        <v>-0.03258702173602046</v>
       </c>
       <c r="D84">
-        <v>61.05576364412495</v>
+        <v>60.69256297826399</v>
       </c>
       <c r="E84">
-        <v>61.97310000000001</v>
+        <v>62.73015000000001</v>
       </c>
       <c r="F84">
-        <v>62.07810000000001</v>
+        <v>62.83515000000001</v>
       </c>
       <c r="G84">
         <v>2.11</v>
@@ -8163,37 +8163,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M84">
-        <v>9.113065080000002</v>
+        <v>9.224200020000001</v>
       </c>
       <c r="N84">
-        <v>-0.7330650800000011</v>
+        <v>-0.8442000200000006</v>
       </c>
       <c r="O84">
-        <v>-0.1832662700000003</v>
+        <v>-0.2110500050000002</v>
       </c>
       <c r="P84">
-        <v>-0.5497988100000009</v>
+        <v>-0.6331500150000005</v>
       </c>
       <c r="Q84">
-        <v>0.05020118999999879</v>
+        <v>-0.03315001500000081</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.67707233781606</v>
+        <v>0.7142060047464165</v>
       </c>
       <c r="T84">
-        <v>6.104885977015645</v>
+        <v>6.463996916840094</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2298897222404122</v>
+        <v>0.2271199665507687</v>
       </c>
       <c r="W84">
-        <v>0.1130521887751075</v>
+        <v>0.1134587889103472</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9195588889616488</v>
+        <v>0.9084798662030747</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2155858156024789</v>
+        <v>0.2165958156024789</v>
       </c>
       <c r="C85">
-        <v>-0.03258702173602046</v>
+        <v>-1.148542117811196</v>
       </c>
       <c r="D85">
-        <v>60.69256297826399</v>
+        <v>60.33365788218881</v>
       </c>
       <c r="E85">
-        <v>62.73015000000001</v>
+        <v>63.48720000000001</v>
       </c>
       <c r="F85">
-        <v>62.83515000000001</v>
+        <v>63.59220000000001</v>
       </c>
       <c r="G85">
         <v>2.11</v>
@@ -8245,37 +8245,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M85">
-        <v>9.224200020000001</v>
+        <v>9.335334960000001</v>
       </c>
       <c r="N85">
-        <v>-0.8442000200000006</v>
+        <v>-0.9553349600000001</v>
       </c>
       <c r="O85">
-        <v>-0.2110500050000002</v>
+        <v>-0.23883374</v>
       </c>
       <c r="P85">
-        <v>-0.6331500150000005</v>
+        <v>-0.71650122</v>
       </c>
       <c r="Q85">
-        <v>-0.03315001500000081</v>
+        <v>-0.1165012200000004</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7142060047464165</v>
+        <v>0.7559813800430676</v>
       </c>
       <c r="T85">
-        <v>6.463996916840094</v>
+        <v>6.867996724142601</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2271199665507687</v>
+        <v>0.2244161574251643</v>
       </c>
       <c r="W85">
-        <v>0.1134587889103472</v>
+        <v>0.1138557080899859</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9084798662030747</v>
+        <v>0.8976646297006573</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2165958156024789</v>
+        <v>0.2176058156024789</v>
       </c>
       <c r="C86">
-        <v>-1.148542117811189</v>
+        <v>-2.260277401585327</v>
       </c>
       <c r="D86">
-        <v>60.33365788218881</v>
+        <v>59.97897259841467</v>
       </c>
       <c r="E86">
-        <v>63.4872</v>
+        <v>64.24424999999999</v>
       </c>
       <c r="F86">
-        <v>63.5922</v>
+        <v>64.34925</v>
       </c>
       <c r="G86">
         <v>2.11</v>
@@ -8327,37 +8327,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M86">
-        <v>9.335334960000001</v>
+        <v>9.4464699</v>
       </c>
       <c r="N86">
-        <v>-0.9553349600000001</v>
+        <v>-1.0664699</v>
       </c>
       <c r="O86">
-        <v>-0.23883374</v>
+        <v>-0.2666174749999999</v>
       </c>
       <c r="P86">
-        <v>-0.71650122</v>
+        <v>-0.7998524249999996</v>
       </c>
       <c r="Q86">
-        <v>-0.1165012200000004</v>
+        <v>-0.199852425</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7559813800430673</v>
+        <v>0.8033268053792717</v>
       </c>
       <c r="T86">
-        <v>6.867996724142597</v>
+        <v>7.32586317241877</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2244161574251643</v>
+        <v>0.2217759673378095</v>
       </c>
       <c r="W86">
-        <v>0.1138557080899859</v>
+        <v>0.1142432879948096</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8976646297006573</v>
+        <v>0.8871038693512379</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2176058156024789</v>
+        <v>0.2186158156024789</v>
       </c>
       <c r="C87">
-        <v>-2.260277401585327</v>
+        <v>-3.367866859523275</v>
       </c>
       <c r="D87">
-        <v>59.97897259841467</v>
+        <v>59.62843314047673</v>
       </c>
       <c r="E87">
-        <v>64.24424999999999</v>
+        <v>65.0013</v>
       </c>
       <c r="F87">
-        <v>64.34925</v>
+        <v>65.1063</v>
       </c>
       <c r="G87">
         <v>2.11</v>
@@ -8409,37 +8409,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M87">
-        <v>9.4464699</v>
+        <v>9.557604840000002</v>
       </c>
       <c r="N87">
-        <v>-1.0664699</v>
+        <v>-1.177604840000001</v>
       </c>
       <c r="O87">
-        <v>-0.2666174749999999</v>
+        <v>-0.2944012100000002</v>
       </c>
       <c r="P87">
-        <v>-0.7998524249999996</v>
+        <v>-0.8832036300000006</v>
       </c>
       <c r="Q87">
-        <v>-0.199852425</v>
+        <v>-0.2832036300000009</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8033268053792717</v>
+        <v>0.8574358629063625</v>
       </c>
       <c r="T87">
-        <v>7.32586317241877</v>
+        <v>7.849139113305825</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2217759673378095</v>
+        <v>0.2191971770199279</v>
       </c>
       <c r="W87">
-        <v>0.1142432879948096</v>
+        <v>0.1146218544134746</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8871038693512379</v>
+        <v>0.8767887080797117</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2186158156024789</v>
+        <v>0.2196258156024789</v>
       </c>
       <c r="C88">
-        <v>-3.367866859523275</v>
+        <v>-4.471382758521898</v>
       </c>
       <c r="D88">
-        <v>59.62843314047673</v>
+        <v>59.2819672414781</v>
       </c>
       <c r="E88">
-        <v>65.0013</v>
+        <v>65.75834999999999</v>
       </c>
       <c r="F88">
-        <v>65.1063</v>
+        <v>65.86335</v>
       </c>
       <c r="G88">
         <v>2.11</v>
@@ -8491,37 +8491,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M88">
-        <v>9.557604840000002</v>
+        <v>9.668739780000001</v>
       </c>
       <c r="N88">
-        <v>-1.177604840000001</v>
+        <v>-1.28873978</v>
       </c>
       <c r="O88">
-        <v>-0.2944012100000002</v>
+        <v>-0.3221849450000001</v>
       </c>
       <c r="P88">
-        <v>-0.8832036300000006</v>
+        <v>-0.9665548350000002</v>
       </c>
       <c r="Q88">
-        <v>-0.2832036300000009</v>
+        <v>-0.3665548350000005</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8574358629063625</v>
+        <v>0.9198693908222367</v>
       </c>
       <c r="T88">
-        <v>7.849139113305825</v>
+        <v>8.452919045098582</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2191971770199279</v>
+        <v>0.2166776692380897</v>
       </c>
       <c r="W88">
-        <v>0.1146218544134746</v>
+        <v>0.1149917181558485</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8767887080797117</v>
+        <v>0.8667106769523587</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2196258156024789</v>
+        <v>0.2206358156024789</v>
       </c>
       <c r="C89">
-        <v>-4.471382758521898</v>
+        <v>-5.5708956955784</v>
       </c>
       <c r="D89">
-        <v>59.2819672414781</v>
+        <v>58.9395043044216</v>
       </c>
       <c r="E89">
-        <v>65.75834999999999</v>
+        <v>66.5154</v>
       </c>
       <c r="F89">
-        <v>65.86335</v>
+        <v>66.6204</v>
       </c>
       <c r="G89">
         <v>2.11</v>
@@ -8573,37 +8573,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M89">
-        <v>9.668739780000001</v>
+        <v>9.779874720000002</v>
       </c>
       <c r="N89">
-        <v>-1.28873978</v>
+        <v>-1.399874720000001</v>
       </c>
       <c r="O89">
-        <v>-0.3221849450000001</v>
+        <v>-0.3499686800000004</v>
       </c>
       <c r="P89">
-        <v>-0.9665548350000002</v>
+        <v>-1.049906040000001</v>
       </c>
       <c r="Q89">
-        <v>-0.3665548350000005</v>
+        <v>-0.4499060400000015</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9198693908222367</v>
+        <v>0.9927085067240898</v>
       </c>
       <c r="T89">
-        <v>8.452919045098582</v>
+        <v>9.157328965523465</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2166776692380897</v>
+        <v>0.2142154229967477</v>
       </c>
       <c r="W89">
-        <v>0.1149917181558485</v>
+        <v>0.1153531759040775</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8667106769523587</v>
+        <v>0.8568616919869909</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2206358156024789</v>
+        <v>0.2216458156024789</v>
       </c>
       <c r="C90">
-        <v>-5.5708956955784</v>
+        <v>-6.666474645747073</v>
       </c>
       <c r="D90">
-        <v>58.9395043044216</v>
+        <v>58.60097535425292</v>
       </c>
       <c r="E90">
-        <v>66.5154</v>
+        <v>67.27244999999999</v>
       </c>
       <c r="F90">
-        <v>66.6204</v>
+        <v>67.37745</v>
       </c>
       <c r="G90">
         <v>2.11</v>
@@ -8655,37 +8655,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M90">
-        <v>9.779874720000002</v>
+        <v>9.89100966</v>
       </c>
       <c r="N90">
-        <v>-1.399874720000001</v>
+        <v>-1.511009659999999</v>
       </c>
       <c r="O90">
-        <v>-0.3499686800000004</v>
+        <v>-0.3777524149999998</v>
       </c>
       <c r="P90">
-        <v>-1.049906040000001</v>
+        <v>-1.133257244999999</v>
       </c>
       <c r="Q90">
-        <v>-0.4499060400000015</v>
+        <v>-0.5332572449999997</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9927085067240898</v>
+        <v>1.078791098244462</v>
       </c>
       <c r="T90">
-        <v>9.157328965523465</v>
+        <v>9.989813416934687</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2142154229967477</v>
+        <v>0.2118085081316158</v>
       </c>
       <c r="W90">
-        <v>0.1153531759040775</v>
+        <v>0.1157065110062788</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8568616919869909</v>
+        <v>0.8472340325264631</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2216458156024789</v>
+        <v>0.2226558156024789</v>
       </c>
       <c r="C91">
-        <v>-6.666474645747073</v>
+        <v>-7.75818700845295</v>
       </c>
       <c r="D91">
-        <v>58.60097535425292</v>
+        <v>58.26631299154705</v>
       </c>
       <c r="E91">
-        <v>67.27244999999999</v>
+        <v>68.0295</v>
       </c>
       <c r="F91">
-        <v>67.37745</v>
+        <v>68.1345</v>
       </c>
       <c r="G91">
         <v>2.11</v>
@@ -8737,37 +8737,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M91">
-        <v>9.89100966</v>
+        <v>10.0021446</v>
       </c>
       <c r="N91">
-        <v>-1.511009659999999</v>
+        <v>-1.6221446</v>
       </c>
       <c r="O91">
-        <v>-0.3777524149999998</v>
+        <v>-0.4055361500000001</v>
       </c>
       <c r="P91">
-        <v>-1.133257244999999</v>
+        <v>-1.21660845</v>
       </c>
       <c r="Q91">
-        <v>-0.5332572449999997</v>
+        <v>-0.6166084500000006</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.078791098244462</v>
+        <v>1.182090208068908</v>
       </c>
       <c r="T91">
-        <v>9.989813416934687</v>
+        <v>10.98879475862816</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2118085081316158</v>
+        <v>0.2094550802634867</v>
       </c>
       <c r="W91">
-        <v>0.1157065110062788</v>
+        <v>0.1160519942173202</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8472340325264631</v>
+        <v>0.8378203210539468</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2226558156024789</v>
+        <v>0.2236658156024789</v>
       </c>
       <c r="C92">
-        <v>-7.75818700845295</v>
+        <v>-8.84609865222707</v>
       </c>
       <c r="D92">
-        <v>58.26631299154705</v>
+        <v>57.93545134777293</v>
       </c>
       <c r="E92">
-        <v>68.0295</v>
+        <v>68.78654999999999</v>
       </c>
       <c r="F92">
-        <v>68.1345</v>
+        <v>68.89155</v>
       </c>
       <c r="G92">
         <v>2.11</v>
@@ -8819,37 +8819,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M92">
-        <v>10.0021446</v>
+        <v>10.11327954</v>
       </c>
       <c r="N92">
-        <v>-1.6221446</v>
+        <v>-1.73327954</v>
       </c>
       <c r="O92">
-        <v>-0.4055361500000001</v>
+        <v>-0.433319885</v>
       </c>
       <c r="P92">
-        <v>-1.21660845</v>
+        <v>-1.299959655</v>
       </c>
       <c r="Q92">
-        <v>-0.6166084500000006</v>
+        <v>-0.6999596550000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.182090208068908</v>
+        <v>1.30834467563212</v>
       </c>
       <c r="T92">
-        <v>10.98879475862816</v>
+        <v>12.20977195403129</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2094550802634867</v>
+        <v>0.2071533760847671</v>
       </c>
       <c r="W92">
-        <v>0.1160519942173202</v>
+        <v>0.1163898843907562</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8378203210539468</v>
+        <v>0.8286135043390683</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2236658156024789</v>
+        <v>0.224675815602479</v>
       </c>
       <c r="C93">
-        <v>-8.84609865222707</v>
+        <v>-9.930273957926822</v>
       </c>
       <c r="D93">
-        <v>57.93545134777293</v>
+        <v>57.60832604207318</v>
       </c>
       <c r="E93">
-        <v>68.78654999999999</v>
+        <v>69.5436</v>
       </c>
       <c r="F93">
-        <v>68.89155</v>
+        <v>69.6486</v>
       </c>
       <c r="G93">
         <v>2.11</v>
@@ -8901,37 +8901,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M93">
-        <v>10.11327954</v>
+        <v>10.22441448</v>
       </c>
       <c r="N93">
-        <v>-1.73327954</v>
+        <v>-1.844414480000001</v>
       </c>
       <c r="O93">
-        <v>-0.433319885</v>
+        <v>-0.4611036200000003</v>
       </c>
       <c r="P93">
-        <v>-1.299959655</v>
+        <v>-1.383310860000001</v>
       </c>
       <c r="Q93">
-        <v>-0.6999596550000002</v>
+        <v>-0.7833108600000012</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.30834467563212</v>
+        <v>1.466162760086136</v>
       </c>
       <c r="T93">
-        <v>12.20977195403129</v>
+        <v>13.73599344828521</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2071533760847671</v>
+        <v>0.2049017089534109</v>
       </c>
       <c r="W93">
-        <v>0.1163898843907562</v>
+        <v>0.1167204291256393</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8286135043390683</v>
+        <v>0.8196068358136435</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.224675815602479</v>
+        <v>0.2256858156024789</v>
       </c>
       <c r="C94">
-        <v>-9.930273957926822</v>
+        <v>-11.01077586049968</v>
       </c>
       <c r="D94">
-        <v>57.60832604207318</v>
+        <v>57.28487413950032</v>
       </c>
       <c r="E94">
-        <v>69.5436</v>
+        <v>70.30065</v>
       </c>
       <c r="F94">
-        <v>69.6486</v>
+        <v>70.40565000000001</v>
       </c>
       <c r="G94">
         <v>2.11</v>
@@ -8983,37 +8983,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M94">
-        <v>10.22441448</v>
+        <v>10.33554942</v>
       </c>
       <c r="N94">
-        <v>-1.844414480000001</v>
+        <v>-1.955549420000002</v>
       </c>
       <c r="O94">
-        <v>-0.4611036200000003</v>
+        <v>-0.4888873550000006</v>
       </c>
       <c r="P94">
-        <v>-1.383310860000001</v>
+        <v>-1.466662065000002</v>
       </c>
       <c r="Q94">
-        <v>-0.7833108600000012</v>
+        <v>-0.8666620650000021</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.466162760086136</v>
+        <v>1.669071725812727</v>
       </c>
       <c r="T94">
-        <v>13.73599344828521</v>
+        <v>15.69827822661166</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2049017089534109</v>
+        <v>0.2026984647711161</v>
       </c>
       <c r="W94">
-        <v>0.1167204291256393</v>
+        <v>0.1170438653716002</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8196068358136435</v>
+        <v>0.8107938590844644</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2256858156024789</v>
+        <v>0.2266958156024789</v>
       </c>
       <c r="C95">
-        <v>-11.01077586049968</v>
+        <v>-12.08766588934832</v>
       </c>
       <c r="D95">
-        <v>57.28487413950032</v>
+        <v>56.96503411065168</v>
       </c>
       <c r="E95">
-        <v>70.30065</v>
+        <v>71.0577</v>
       </c>
       <c r="F95">
-        <v>70.40565000000001</v>
+        <v>71.1627</v>
       </c>
       <c r="G95">
         <v>2.11</v>
@@ -9065,37 +9065,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M95">
-        <v>10.33554942</v>
+        <v>10.44668436</v>
       </c>
       <c r="N95">
-        <v>-1.955549420000002</v>
+        <v>-2.06668436</v>
       </c>
       <c r="O95">
-        <v>-0.4888873550000006</v>
+        <v>-0.51667109</v>
       </c>
       <c r="P95">
-        <v>-1.466662065000002</v>
+        <v>-1.55001327</v>
       </c>
       <c r="Q95">
-        <v>-0.8666620650000021</v>
+        <v>-0.9500132700000004</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.669071725812727</v>
+        <v>1.939617013448181</v>
       </c>
       <c r="T95">
-        <v>15.69827822661166</v>
+        <v>18.31465793104694</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2026984647711161</v>
+        <v>0.2005420981246149</v>
       </c>
       <c r="W95">
-        <v>0.1170438653716002</v>
+        <v>0.1173604199953066</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8107938590844644</v>
+        <v>0.8021683924984597</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2266958156024789</v>
+        <v>0.2861043603138095</v>
       </c>
       <c r="C96">
-        <v>-12.08766588934832</v>
+        <v>-26.92773032789508</v>
       </c>
       <c r="D96">
-        <v>56.96503411065168</v>
+        <v>42.88201967210492</v>
       </c>
       <c r="E96">
-        <v>71.0577</v>
+        <v>71.81475</v>
       </c>
       <c r="F96">
-        <v>71.1627</v>
+        <v>71.91975000000001</v>
       </c>
       <c r="G96">
         <v>2.11</v>
@@ -9147,45 +9147,45 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M96">
-        <v>10.44668436</v>
+        <v>14.4414858</v>
       </c>
       <c r="N96">
-        <v>-2.06668436</v>
+        <v>-6.061485800000002</v>
       </c>
       <c r="O96">
-        <v>-0.51667109</v>
+        <v>-1.51537145</v>
       </c>
       <c r="P96">
-        <v>-1.55001327</v>
+        <v>-4.546114350000002</v>
       </c>
       <c r="Q96">
-        <v>-0.9500132700000004</v>
+        <v>-3.946114350000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.939617013448181</v>
+        <v>2.460351310364429</v>
       </c>
       <c r="T96">
-        <v>18.31465793104694</v>
+        <v>23.35055657028276</v>
       </c>
       <c r="U96">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.2005420981246149</v>
+        <v>0.1450681757413077</v>
       </c>
       <c r="W96">
-        <v>0.1173604199953066</v>
+        <v>0.1716703103111454</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.8021683924984597</v>
+        <v>0.5802727029652308</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2861043603138095</v>
+        <v>0.2876543603138095</v>
       </c>
       <c r="C97">
-        <v>-26.92773032789508</v>
+        <v>-27.95960328500662</v>
       </c>
       <c r="D97">
-        <v>42.88201967210492</v>
+        <v>42.60719671499338</v>
       </c>
       <c r="E97">
-        <v>71.81475</v>
+        <v>72.5718</v>
       </c>
       <c r="F97">
-        <v>71.91975000000001</v>
+        <v>72.6768</v>
       </c>
       <c r="G97">
         <v>2.11</v>
@@ -9229,37 +9229,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M97">
-        <v>14.4414858</v>
+        <v>14.59350144</v>
       </c>
       <c r="N97">
-        <v>-6.061485800000002</v>
+        <v>-6.21350144</v>
       </c>
       <c r="O97">
-        <v>-1.51537145</v>
+        <v>-1.55337536</v>
       </c>
       <c r="P97">
-        <v>-4.546114350000002</v>
+        <v>-4.66012608</v>
       </c>
       <c r="Q97">
-        <v>-3.946114350000002</v>
+        <v>-4.06012608</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.460351310364429</v>
+        <v>3.063989137955538</v>
       </c>
       <c r="T97">
-        <v>23.35055657028276</v>
+        <v>29.18819571285346</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1450681757413077</v>
+        <v>0.1435570489106691</v>
       </c>
       <c r="W97">
-        <v>0.1716703103111454</v>
+        <v>0.1719737445787377</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5802727029652308</v>
+        <v>0.5742281956426765</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2876543603138095</v>
+        <v>0.2892043603138094</v>
       </c>
       <c r="C98">
-        <v>-27.95960328500662</v>
+        <v>-28.98797609460252</v>
       </c>
       <c r="D98">
-        <v>42.60719671499338</v>
+        <v>42.33587390539748</v>
       </c>
       <c r="E98">
-        <v>72.5718</v>
+        <v>73.32884999999999</v>
       </c>
       <c r="F98">
-        <v>72.6768</v>
+        <v>73.43384999999999</v>
       </c>
       <c r="G98">
         <v>2.11</v>
@@ -9311,37 +9311,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M98">
-        <v>14.59350144</v>
+        <v>14.74551708</v>
       </c>
       <c r="N98">
-        <v>-6.21350144</v>
+        <v>-6.365517079999998</v>
       </c>
       <c r="O98">
-        <v>-1.55337536</v>
+        <v>-1.59137927</v>
       </c>
       <c r="P98">
-        <v>-4.66012608</v>
+        <v>-4.774137809999999</v>
       </c>
       <c r="Q98">
-        <v>-4.06012608</v>
+        <v>-4.17413781</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.06398913795553</v>
+        <v>4.070052183940707</v>
       </c>
       <c r="T98">
-        <v>29.18819571285338</v>
+        <v>38.9175942838045</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1435570489106691</v>
+        <v>0.1420770793342705</v>
       </c>
       <c r="W98">
-        <v>0.1719737445787377</v>
+        <v>0.1722709224696785</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5742281956426765</v>
+        <v>0.568308317337082</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2892043603138094</v>
+        <v>0.2907543603138095</v>
       </c>
       <c r="C99">
-        <v>-28.98797609460252</v>
+        <v>-30.01291520043147</v>
       </c>
       <c r="D99">
-        <v>42.33587390539748</v>
+        <v>42.06798479956853</v>
       </c>
       <c r="E99">
-        <v>73.32884999999999</v>
+        <v>74.0859</v>
       </c>
       <c r="F99">
-        <v>73.43384999999999</v>
+        <v>74.1909</v>
       </c>
       <c r="G99">
         <v>2.11</v>
@@ -9393,37 +9393,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M99">
-        <v>14.74551708</v>
+        <v>14.89753272</v>
       </c>
       <c r="N99">
-        <v>-6.365517079999998</v>
+        <v>-6.51753272</v>
       </c>
       <c r="O99">
-        <v>-1.59137927</v>
+        <v>-1.62938318</v>
       </c>
       <c r="P99">
-        <v>-4.774137809999999</v>
+        <v>-4.888149540000001</v>
       </c>
       <c r="Q99">
-        <v>-4.17413781</v>
+        <v>-4.288149540000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.070052183940707</v>
+        <v>6.082178275911061</v>
       </c>
       <c r="T99">
-        <v>38.9175942838045</v>
+        <v>58.37639142570676</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1420770793342705</v>
+        <v>0.1406273132186146</v>
       </c>
       <c r="W99">
-        <v>0.1722709224696785</v>
+        <v>0.1725620355057022</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.568308317337082</v>
+        <v>0.5625092528744585</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2907543603138095</v>
+        <v>0.2923043603138095</v>
       </c>
       <c r="C100">
-        <v>-30.01291520043147</v>
+        <v>-31.03448537506985</v>
       </c>
       <c r="D100">
-        <v>42.06798479956853</v>
+        <v>41.80346462493014</v>
       </c>
       <c r="E100">
-        <v>74.0859</v>
+        <v>74.84294999999999</v>
       </c>
       <c r="F100">
-        <v>74.1909</v>
+        <v>74.94794999999999</v>
       </c>
       <c r="G100">
         <v>2.11</v>
@@ -9475,37 +9475,37 @@
         <v>8.380000000000001</v>
       </c>
       <c r="M100">
-        <v>14.89753272</v>
+        <v>15.04954836</v>
       </c>
       <c r="N100">
-        <v>-6.51753272</v>
+        <v>-6.669548359999999</v>
       </c>
       <c r="O100">
-        <v>-1.62938318</v>
+        <v>-1.66738709</v>
       </c>
       <c r="P100">
-        <v>-4.888149540000001</v>
+        <v>-5.002161269999998</v>
       </c>
       <c r="Q100">
-        <v>-4.288149540000001</v>
+        <v>-4.402161269999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>6.082178275911061</v>
+        <v>12.11855655182212</v>
       </c>
       <c r="T100">
-        <v>58.37639142570676</v>
+        <v>116.7527828514135</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1406273132186146</v>
+        <v>0.1392068353073155</v>
       </c>
       <c r="W100">
-        <v>0.1725620355057022</v>
+        <v>0.1728472674702911</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5625092528744585</v>
+        <v>0.556827341229262</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2923043603138095</v>
-      </c>
-      <c r="C101">
-        <v>-31.03448537506985</v>
-      </c>
-      <c r="D101">
-        <v>41.80346462493014</v>
-      </c>
-      <c r="E101">
-        <v>74.84294999999999</v>
-      </c>
-      <c r="F101">
-        <v>74.94794999999999</v>
-      </c>
-      <c r="G101">
-        <v>2.11</v>
-      </c>
-      <c r="H101">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.98</v>
-      </c>
-      <c r="K101">
-        <v>0.5999999999999996</v>
-      </c>
-      <c r="L101">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="M101">
-        <v>15.04954836</v>
-      </c>
-      <c r="N101">
-        <v>-6.669548359999999</v>
-      </c>
-      <c r="O101">
-        <v>-1.66738709</v>
-      </c>
-      <c r="P101">
-        <v>-5.002161269999998</v>
-      </c>
-      <c r="Q101">
-        <v>-4.402161269999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>12.11855655182212</v>
-      </c>
-      <c r="T101">
-        <v>116.7527828514135</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1392068353073155</v>
-      </c>
-      <c r="W101">
-        <v>0.1728472674702911</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.556827341229262</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
